--- a/research/traditional_assets/database/data/lithuania/lithuania_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_software_entertainment.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1197352269442164</v>
+        <v>0.1195938741038001</v>
       </c>
       <c r="C2">
-        <v>1945.084745176576</v>
+        <v>1929.296366770793</v>
       </c>
       <c r="D2">
-        <v>1921.484745176576</v>
+        <v>1925.165366770793</v>
       </c>
       <c r="E2">
-        <v>-49.2</v>
+        <v>-29.731</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.469</v>
       </c>
       <c r="G2">
         <v>23.6</v>
@@ -1445,28 +1445,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9792907</v>
       </c>
       <c r="N2">
-        <v>48.90000000000001</v>
+        <v>47.92070930000001</v>
       </c>
       <c r="O2">
-        <v>7.335000000000001</v>
+        <v>7.188106395000001</v>
       </c>
       <c r="P2">
-        <v>41.565</v>
+        <v>40.73260290500001</v>
       </c>
       <c r="Q2">
-        <v>57.86500000000001</v>
+        <v>57.032602905</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1197352269442164</v>
+        <v>0.1203700243472728</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.365776183831158</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>49.9341002625676</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1195938741038001</v>
+        <v>0.1194525212633838</v>
       </c>
       <c r="C3">
-        <v>1929.296366770793</v>
+        <v>1913.522115955156</v>
       </c>
       <c r="D3">
-        <v>1925.165366770793</v>
+        <v>1928.860115955156</v>
       </c>
       <c r="E3">
-        <v>-29.731</v>
+        <v>-10.262</v>
       </c>
       <c r="F3">
-        <v>19.469</v>
+        <v>38.938</v>
       </c>
       <c r="G3">
         <v>23.6</v>
@@ -1527,28 +1527,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M3">
-        <v>0.9792907</v>
+        <v>1.9585814</v>
       </c>
       <c r="N3">
-        <v>47.92070930000001</v>
+        <v>46.94141860000001</v>
       </c>
       <c r="O3">
-        <v>7.188106395000001</v>
+        <v>7.04121279</v>
       </c>
       <c r="P3">
-        <v>40.73260290500001</v>
+        <v>39.90020581</v>
       </c>
       <c r="Q3">
-        <v>57.032602905</v>
+        <v>56.20020581</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1203700243472728</v>
+        <v>0.1210177767993712</v>
       </c>
       <c r="T3">
-        <v>1.365776183831158</v>
+        <v>1.377639997472605</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>49.9341002625676</v>
+        <v>24.9670501312838</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1194525212633838</v>
+        <v>0.1193111684229674</v>
       </c>
       <c r="C4">
-        <v>1913.522115955156</v>
+        <v>1897.762074226466</v>
       </c>
       <c r="D4">
-        <v>1928.860115955156</v>
+        <v>1932.569074226466</v>
       </c>
       <c r="E4">
-        <v>-10.262</v>
+        <v>9.207000000000001</v>
       </c>
       <c r="F4">
-        <v>38.938</v>
+        <v>58.407</v>
       </c>
       <c r="G4">
         <v>23.6</v>
@@ -1609,28 +1609,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M4">
-        <v>1.9585814</v>
+        <v>2.9378721</v>
       </c>
       <c r="N4">
-        <v>46.94141860000001</v>
+        <v>45.96212790000001</v>
       </c>
       <c r="O4">
-        <v>7.04121279</v>
+        <v>6.894319185000001</v>
       </c>
       <c r="P4">
-        <v>39.90020581</v>
+        <v>39.06780871500001</v>
       </c>
       <c r="Q4">
-        <v>56.20020581</v>
+        <v>55.36780871500001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1210177767993712</v>
+        <v>0.1216788849721314</v>
       </c>
       <c r="T4">
-        <v>1.377639997472605</v>
+        <v>1.389748425828309</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>24.9670501312838</v>
+        <v>16.64470008752253</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1193111684229674</v>
+        <v>0.1192208155825511</v>
       </c>
       <c r="C5">
-        <v>1897.762074226466</v>
+        <v>1880.671324914253</v>
       </c>
       <c r="D5">
-        <v>1932.569074226466</v>
+        <v>1934.947324914253</v>
       </c>
       <c r="E5">
-        <v>9.207000000000001</v>
+        <v>28.676</v>
       </c>
       <c r="F5">
-        <v>58.407</v>
+        <v>77.876</v>
       </c>
       <c r="G5">
         <v>23.6</v>
@@ -1691,45 +1691,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M5">
-        <v>2.9378721</v>
+        <v>4.0339768</v>
       </c>
       <c r="N5">
-        <v>45.96212790000001</v>
+        <v>44.86602320000001</v>
       </c>
       <c r="O5">
-        <v>6.894319185000001</v>
+        <v>6.729903480000001</v>
       </c>
       <c r="P5">
-        <v>39.06780871500001</v>
+        <v>38.13611972000001</v>
       </c>
       <c r="Q5">
-        <v>55.36780871500001</v>
+        <v>54.43611972000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1216788849721314</v>
+        <v>0.1223537662318241</v>
       </c>
       <c r="T5">
-        <v>1.389748425828309</v>
+        <v>1.402109113108089</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.15</v>
       </c>
       <c r="W5">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>16.64470008752253</v>
+        <v>12.12203302706154</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1192208155825511</v>
+        <v>0.1191644627421348</v>
       </c>
       <c r="C6">
-        <v>1880.671324914253</v>
+        <v>1862.688600063546</v>
       </c>
       <c r="D6">
-        <v>1934.947324914253</v>
+        <v>1936.433600063546</v>
       </c>
       <c r="E6">
-        <v>28.676</v>
+        <v>48.14500000000001</v>
       </c>
       <c r="F6">
-        <v>77.876</v>
+        <v>97.34500000000001</v>
       </c>
       <c r="G6">
         <v>23.6</v>
@@ -1773,45 +1773,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M6">
-        <v>4.0339768</v>
+        <v>5.207957500000001</v>
       </c>
       <c r="N6">
-        <v>44.86602320000001</v>
+        <v>43.69204250000001</v>
       </c>
       <c r="O6">
-        <v>6.729903480000001</v>
+        <v>6.553806375000001</v>
       </c>
       <c r="P6">
-        <v>38.13611972000001</v>
+        <v>37.13823612500001</v>
       </c>
       <c r="Q6">
-        <v>54.43611972000001</v>
+        <v>53.438236125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1223537662318241</v>
+        <v>0.1230428555180366</v>
       </c>
       <c r="T6">
-        <v>1.402109113108089</v>
+        <v>1.414730025383234</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.15</v>
       </c>
       <c r="W6">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>12.12203302706154</v>
+        <v>9.389477544699625</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1191644627421348</v>
+        <v>0.1190503099017184</v>
       </c>
       <c r="C7">
-        <v>1862.688600063546</v>
+        <v>1846.237326487114</v>
       </c>
       <c r="D7">
-        <v>1936.433600063546</v>
+        <v>1939.451326487114</v>
       </c>
       <c r="E7">
-        <v>48.14500000000001</v>
+        <v>67.61400000000002</v>
       </c>
       <c r="F7">
-        <v>97.34500000000001</v>
+        <v>116.814</v>
       </c>
       <c r="G7">
         <v>23.6</v>
@@ -1855,28 +1855,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M7">
-        <v>5.207957500000001</v>
+        <v>6.249549000000001</v>
       </c>
       <c r="N7">
-        <v>43.69204250000001</v>
+        <v>42.650451</v>
       </c>
       <c r="O7">
-        <v>6.553806375000001</v>
+        <v>6.39756765</v>
       </c>
       <c r="P7">
-        <v>37.13823612500001</v>
+        <v>36.25288335</v>
       </c>
       <c r="Q7">
-        <v>53.438236125</v>
+        <v>52.55288335</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1230428555180366</v>
+        <v>0.1237466062784239</v>
       </c>
       <c r="T7">
-        <v>1.414730025383234</v>
+        <v>1.427619467706785</v>
       </c>
       <c r="U7">
         <v>0.0535</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>9.389477544699625</v>
+        <v>7.824564620583021</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1190503099017184</v>
+        <v>0.1189837570613021</v>
       </c>
       <c r="C8">
-        <v>1846.237326487114</v>
+        <v>1828.532051114134</v>
       </c>
       <c r="D8">
-        <v>1939.451326487114</v>
+        <v>1941.215051114134</v>
       </c>
       <c r="E8">
-        <v>67.614</v>
+        <v>87.08299999999998</v>
       </c>
       <c r="F8">
-        <v>116.814</v>
+        <v>136.283</v>
       </c>
       <c r="G8">
         <v>23.6</v>
@@ -1937,45 +1937,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M8">
-        <v>6.249549</v>
+        <v>7.400166899999999</v>
       </c>
       <c r="N8">
-        <v>42.650451</v>
+        <v>41.4998331</v>
       </c>
       <c r="O8">
-        <v>6.39756765</v>
+        <v>6.224974965</v>
       </c>
       <c r="P8">
-        <v>36.25288335</v>
+        <v>35.274858135</v>
       </c>
       <c r="Q8">
-        <v>52.55288335</v>
+        <v>51.574858135</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1237466062784239</v>
+        <v>0.1244654914637657</v>
       </c>
       <c r="T8">
-        <v>1.427619467706785</v>
+        <v>1.44078610233837</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.15</v>
       </c>
       <c r="W8">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.824564620583022</v>
+        <v>6.607959071842016</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1189837570613021</v>
+        <v>0.1189444042208858</v>
       </c>
       <c r="C9">
-        <v>1828.532051114134</v>
+        <v>1810.107455357137</v>
       </c>
       <c r="D9">
-        <v>1941.215051114134</v>
+        <v>1942.259455357137</v>
       </c>
       <c r="E9">
-        <v>87.08300000000001</v>
+        <v>106.552</v>
       </c>
       <c r="F9">
-        <v>136.283</v>
+        <v>155.752</v>
       </c>
       <c r="G9">
         <v>23.6</v>
@@ -2019,45 +2019,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M9">
-        <v>7.400166900000001</v>
+        <v>8.613085600000002</v>
       </c>
       <c r="N9">
-        <v>41.4998331</v>
+        <v>40.2869144</v>
       </c>
       <c r="O9">
-        <v>6.224974965</v>
+        <v>6.04303716</v>
       </c>
       <c r="P9">
-        <v>35.274858135</v>
+        <v>34.24387724</v>
       </c>
       <c r="Q9">
-        <v>51.574858135</v>
+        <v>50.54387724</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1244654914637657</v>
+        <v>0.1252000045879194</v>
       </c>
       <c r="T9">
-        <v>1.44078610233837</v>
+        <v>1.454238968157598</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.15</v>
       </c>
       <c r="W9">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.607959071842014</v>
+        <v>5.677407873433882</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1189444042208858</v>
+        <v>0.1188455513804695</v>
       </c>
       <c r="C10">
-        <v>1810.107455357137</v>
+        <v>1793.266922941528</v>
       </c>
       <c r="D10">
-        <v>1942.259455357137</v>
+        <v>1944.887922941528</v>
       </c>
       <c r="E10">
-        <v>106.552</v>
+        <v>126.021</v>
       </c>
       <c r="F10">
-        <v>155.752</v>
+        <v>175.221</v>
       </c>
       <c r="G10">
         <v>23.6</v>
@@ -2101,28 +2101,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M10">
-        <v>8.613085600000002</v>
+        <v>9.6897213</v>
       </c>
       <c r="N10">
-        <v>40.2869144</v>
+        <v>39.2102787</v>
       </c>
       <c r="O10">
-        <v>6.04303716</v>
+        <v>5.881541805</v>
       </c>
       <c r="P10">
-        <v>34.24387724</v>
+        <v>33.32873689500001</v>
       </c>
       <c r="Q10">
-        <v>50.54387724</v>
+        <v>49.628736895</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1252000045879194</v>
+        <v>0.1259506608576588</v>
       </c>
       <c r="T10">
-        <v>1.454238968157598</v>
+        <v>1.467987501357469</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.677407873433882</v>
+        <v>5.046584776385674</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1188455513804695</v>
+        <v>0.1187466985400532</v>
       </c>
       <c r="C11">
-        <v>1793.266922941528</v>
+        <v>1776.433514398331</v>
       </c>
       <c r="D11">
-        <v>1944.887922941528</v>
+        <v>1947.523514398332</v>
       </c>
       <c r="E11">
-        <v>126.021</v>
+        <v>145.49</v>
       </c>
       <c r="F11">
-        <v>175.221</v>
+        <v>194.69</v>
       </c>
       <c r="G11">
         <v>23.6</v>
@@ -2183,28 +2183,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M11">
-        <v>9.6897213</v>
+        <v>10.766357</v>
       </c>
       <c r="N11">
-        <v>39.2102787</v>
+        <v>38.13364300000001</v>
       </c>
       <c r="O11">
-        <v>5.881541805</v>
+        <v>5.720046450000001</v>
       </c>
       <c r="P11">
-        <v>33.32873689500001</v>
+        <v>32.41359655000001</v>
       </c>
       <c r="Q11">
-        <v>49.628736895</v>
+        <v>48.71359655000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1259506608576588</v>
+        <v>0.1267179983778368</v>
       </c>
       <c r="T11">
-        <v>1.467987501357469</v>
+        <v>1.482041557517336</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.046584776385674</v>
+        <v>4.541926298747107</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1187466985400532</v>
+        <v>0.1192088456996368</v>
       </c>
       <c r="C12">
-        <v>1776.433514398331</v>
+        <v>1744.703833116347</v>
       </c>
       <c r="D12">
-        <v>1947.523514398332</v>
+        <v>1935.262833116347</v>
       </c>
       <c r="E12">
-        <v>145.49</v>
+        <v>164.959</v>
       </c>
       <c r="F12">
-        <v>194.69</v>
+        <v>214.159</v>
       </c>
       <c r="G12">
         <v>23.6</v>
@@ -2265,45 +2265,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M12">
-        <v>10.766357</v>
+        <v>13.1279467</v>
       </c>
       <c r="N12">
-        <v>38.13364300000001</v>
+        <v>35.7720533</v>
       </c>
       <c r="O12">
-        <v>5.720046450000001</v>
+        <v>5.365807995</v>
       </c>
       <c r="P12">
-        <v>32.41359655000001</v>
+        <v>30.406245305</v>
       </c>
       <c r="Q12">
-        <v>48.71359655000001</v>
+        <v>46.706245305</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1267179983778368</v>
+        <v>0.1275025794377942</v>
       </c>
       <c r="T12">
-        <v>1.482041557517336</v>
+        <v>1.496411435163943</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.15</v>
       </c>
       <c r="W12">
-        <v>0.047005</v>
+        <v>0.052105</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.541926298747107</v>
+        <v>3.724878011578155</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1192088456996368</v>
+        <v>0.1194465928592205</v>
       </c>
       <c r="C13">
-        <v>1744.703833116347</v>
+        <v>1718.987385355923</v>
       </c>
       <c r="D13">
-        <v>1935.262833116347</v>
+        <v>1929.015385355923</v>
       </c>
       <c r="E13">
-        <v>164.959</v>
+        <v>184.428</v>
       </c>
       <c r="F13">
-        <v>214.159</v>
+        <v>233.628</v>
       </c>
       <c r="G13">
         <v>23.6</v>
@@ -2347,45 +2347,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M13">
-        <v>13.1279467</v>
+        <v>14.9755548</v>
       </c>
       <c r="N13">
-        <v>35.7720533</v>
+        <v>33.92444520000001</v>
       </c>
       <c r="O13">
-        <v>5.365807995</v>
+        <v>5.088666780000001</v>
       </c>
       <c r="P13">
-        <v>30.406245305</v>
+        <v>28.83577842000001</v>
       </c>
       <c r="Q13">
-        <v>46.706245305</v>
+        <v>45.13577842000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1275025794377942</v>
+        <v>0.1283049918854778</v>
       </c>
       <c r="T13">
-        <v>1.496411435163943</v>
+        <v>1.511107900938881</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.724878011578155</v>
+        <v>3.265321429026456</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1194465928592205</v>
+        <v>0.1194225400188042</v>
       </c>
       <c r="C14">
-        <v>1718.987385355923</v>
+        <v>1700.148604025542</v>
       </c>
       <c r="D14">
-        <v>1929.015385355923</v>
+        <v>1929.645604025542</v>
       </c>
       <c r="E14">
-        <v>184.428</v>
+        <v>203.897</v>
       </c>
       <c r="F14">
-        <v>233.628</v>
+        <v>253.097</v>
       </c>
       <c r="G14">
         <v>23.6</v>
@@ -2429,28 +2429,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M14">
-        <v>14.9755548</v>
+        <v>16.2235177</v>
       </c>
       <c r="N14">
-        <v>33.92444520000001</v>
+        <v>32.6764823</v>
       </c>
       <c r="O14">
-        <v>5.088666780000001</v>
+        <v>4.901472345</v>
       </c>
       <c r="P14">
-        <v>28.83577842000001</v>
+        <v>27.775009955</v>
       </c>
       <c r="Q14">
-        <v>45.13577842000001</v>
+        <v>44.075009955</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1283049918854778</v>
+        <v>0.1291258505963266</v>
       </c>
       <c r="T14">
-        <v>1.511107900938881</v>
+        <v>1.526142216501749</v>
       </c>
       <c r="U14">
         <v>0.0641</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.265321429026456</v>
+        <v>3.014142857562882</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1194225400188042</v>
+        <v>0.1207907871783879</v>
       </c>
       <c r="C15">
-        <v>1700.148604025542</v>
+        <v>1645.472184340367</v>
       </c>
       <c r="D15">
-        <v>1929.645604025542</v>
+        <v>1894.438184340367</v>
       </c>
       <c r="E15">
-        <v>203.897</v>
+        <v>223.366</v>
       </c>
       <c r="F15">
-        <v>253.097</v>
+        <v>272.566</v>
       </c>
       <c r="G15">
         <v>23.6</v>
@@ -2511,45 +2511,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M15">
-        <v>16.2235177</v>
+        <v>20.6605028</v>
       </c>
       <c r="N15">
-        <v>32.6764823</v>
+        <v>28.2394972</v>
       </c>
       <c r="O15">
-        <v>4.901472345</v>
+        <v>4.23592458</v>
       </c>
       <c r="P15">
-        <v>27.775009955</v>
+        <v>24.00357262</v>
       </c>
       <c r="Q15">
-        <v>44.075009955</v>
+        <v>40.30357262</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1291258505963266</v>
+        <v>0.129965799044637</v>
       </c>
       <c r="T15">
-        <v>1.526142216501749</v>
+        <v>1.541526167310264</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.054485</v>
+        <v>0.06443</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.014142857562882</v>
+        <v>2.366834944597766</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1207907871783879</v>
+        <v>0.1208661843379715</v>
       </c>
       <c r="C16">
-        <v>1645.472184340367</v>
+        <v>1624.100393365099</v>
       </c>
       <c r="D16">
-        <v>1894.438184340367</v>
+        <v>1892.535393365099</v>
       </c>
       <c r="E16">
-        <v>223.366</v>
+        <v>242.8350000000001</v>
       </c>
       <c r="F16">
-        <v>272.566</v>
+        <v>292.0350000000001</v>
       </c>
       <c r="G16">
         <v>23.6</v>
@@ -2593,28 +2593,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M16">
-        <v>20.6605028</v>
+        <v>22.13625300000001</v>
       </c>
       <c r="N16">
-        <v>28.2394972</v>
+        <v>26.763747</v>
       </c>
       <c r="O16">
-        <v>4.23592458</v>
+        <v>4.014562049999999</v>
       </c>
       <c r="P16">
-        <v>24.00357262</v>
+        <v>22.74918495</v>
       </c>
       <c r="Q16">
-        <v>40.30357262</v>
+        <v>39.04918495</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.129965799044637</v>
+        <v>0.1308255109858489</v>
       </c>
       <c r="T16">
-        <v>1.541526167310264</v>
+        <v>1.557272093431922</v>
       </c>
       <c r="U16">
         <v>0.07580000000000001</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.366834944597766</v>
+        <v>2.209045948291248</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1208661843379715</v>
+        <v>0.1209415814975552</v>
       </c>
       <c r="C17">
-        <v>1624.100393365099</v>
+        <v>1602.732420915657</v>
       </c>
       <c r="D17">
-        <v>1892.535393365099</v>
+        <v>1890.636420915657</v>
       </c>
       <c r="E17">
-        <v>242.835</v>
+        <v>262.304</v>
       </c>
       <c r="F17">
-        <v>292.035</v>
+        <v>311.504</v>
       </c>
       <c r="G17">
         <v>23.6</v>
@@ -2675,28 +2675,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M17">
-        <v>22.136253</v>
+        <v>23.6120032</v>
       </c>
       <c r="N17">
-        <v>26.763747</v>
+        <v>25.2879968</v>
       </c>
       <c r="O17">
-        <v>4.01456205</v>
+        <v>3.79319952</v>
       </c>
       <c r="P17">
-        <v>22.74918495</v>
+        <v>21.49479728</v>
       </c>
       <c r="Q17">
-        <v>39.04918495</v>
+        <v>37.79479728</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1308255109858489</v>
+        <v>0.1317056922589943</v>
       </c>
       <c r="T17">
-        <v>1.557272093431922</v>
+        <v>1.573392922556476</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.209045948291249</v>
+        <v>2.070980576523046</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1209415814975552</v>
+        <v>0.1230688786571389</v>
       </c>
       <c r="C18">
-        <v>1602.732420915657</v>
+        <v>1531.212122153245</v>
       </c>
       <c r="D18">
-        <v>1890.636420915657</v>
+        <v>1838.585122153245</v>
       </c>
       <c r="E18">
-        <v>262.304</v>
+        <v>281.773</v>
       </c>
       <c r="F18">
-        <v>311.504</v>
+        <v>330.973</v>
       </c>
       <c r="G18">
         <v>23.6</v>
@@ -2757,45 +2757,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M18">
-        <v>23.6120032</v>
+        <v>29.78757</v>
       </c>
       <c r="N18">
-        <v>25.2879968</v>
+        <v>19.11243000000001</v>
       </c>
       <c r="O18">
-        <v>3.79319952</v>
+        <v>2.866864500000001</v>
       </c>
       <c r="P18">
-        <v>21.49479728</v>
+        <v>16.2455655</v>
       </c>
       <c r="Q18">
-        <v>37.79479728</v>
+        <v>32.54556550000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1317056922589943</v>
+        <v>0.1326070827194444</v>
       </c>
       <c r="T18">
-        <v>1.573392922556476</v>
+        <v>1.589902205394875</v>
       </c>
       <c r="U18">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V18">
         <v>0.15</v>
       </c>
       <c r="W18">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.070980576523046</v>
+        <v>1.641624341965458</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1230688786571389</v>
+        <v>0.1232649758167225</v>
       </c>
       <c r="C19">
-        <v>1531.212122153245</v>
+        <v>1507.088872715924</v>
       </c>
       <c r="D19">
-        <v>1838.585122153245</v>
+        <v>1833.930872715924</v>
       </c>
       <c r="E19">
-        <v>281.773</v>
+        <v>301.2420000000001</v>
       </c>
       <c r="F19">
-        <v>330.973</v>
+        <v>350.4420000000001</v>
       </c>
       <c r="G19">
         <v>23.6</v>
@@ -2839,28 +2839,28 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M19">
-        <v>29.78757</v>
+        <v>31.53978</v>
       </c>
       <c r="N19">
-        <v>19.11243000000001</v>
+        <v>17.36022</v>
       </c>
       <c r="O19">
-        <v>2.866864500000001</v>
+        <v>2.604033</v>
       </c>
       <c r="P19">
-        <v>16.2455655</v>
+        <v>14.756187</v>
       </c>
       <c r="Q19">
-        <v>32.54556550000001</v>
+        <v>31.056187</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1326070827194444</v>
+        <v>0.1335304583130763</v>
       </c>
       <c r="T19">
-        <v>1.589902205394875</v>
+        <v>1.606814153668356</v>
       </c>
       <c r="U19">
         <v>0.09</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.641624341965458</v>
+        <v>1.550422989634043</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1232649758167226</v>
+        <v>0.1332601988906902</v>
       </c>
       <c r="C20">
-        <v>1507.088872715924</v>
+        <v>1278.032558628728</v>
       </c>
       <c r="D20">
-        <v>1833.930872715924</v>
+        <v>1624.343558628728</v>
       </c>
       <c r="E20">
-        <v>301.242</v>
+        <v>320.711</v>
       </c>
       <c r="F20">
-        <v>350.442</v>
+        <v>369.911</v>
       </c>
       <c r="G20">
         <v>23.6</v>
@@ -2921,45 +2921,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M20">
-        <v>31.53978</v>
+        <v>54.3029348</v>
       </c>
       <c r="N20">
-        <v>17.36022000000001</v>
+        <v>-5.402934799999997</v>
       </c>
       <c r="O20">
-        <v>2.604033000000001</v>
+        <v>-0.8104402199999995</v>
       </c>
       <c r="P20">
-        <v>14.756187</v>
+        <v>-4.592494579999998</v>
       </c>
       <c r="Q20">
-        <v>31.056187</v>
+        <v>11.70750542</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1335304583130763</v>
+        <v>0.134735465130248</v>
       </c>
       <c r="T20">
-        <v>1.606814153668356</v>
+        <v>1.628884276705771</v>
       </c>
       <c r="U20">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.15</v>
+        <v>0.1350755723795613</v>
       </c>
       <c r="W20">
-        <v>0.0765</v>
+        <v>0.1269709059746804</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.550422989634043</v>
+        <v>0.9005038158637423</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1332601988906902</v>
+        <v>0.1342701988906901</v>
       </c>
       <c r="C21">
-        <v>1278.032558628728</v>
+        <v>1240.019608069263</v>
       </c>
       <c r="D21">
-        <v>1624.343558628728</v>
+        <v>1605.799608069263</v>
       </c>
       <c r="E21">
-        <v>320.711</v>
+        <v>340.1800000000001</v>
       </c>
       <c r="F21">
-        <v>369.911</v>
+        <v>389.3800000000001</v>
       </c>
       <c r="G21">
         <v>23.6</v>
@@ -3003,37 +3003,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M21">
-        <v>54.3029348</v>
+        <v>57.16098400000001</v>
       </c>
       <c r="N21">
-        <v>-5.402934799999997</v>
+        <v>-8.260984000000008</v>
       </c>
       <c r="O21">
-        <v>-0.8104402199999995</v>
+        <v>-1.239147600000001</v>
       </c>
       <c r="P21">
-        <v>-4.592494579999998</v>
+        <v>-7.021836400000007</v>
       </c>
       <c r="Q21">
-        <v>11.70750542</v>
+        <v>9.278163599999994</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.134735465130248</v>
+        <v>0.1358471584443761</v>
       </c>
       <c r="T21">
-        <v>1.628884276705771</v>
+        <v>1.649245330164593</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.1350755723795613</v>
+        <v>0.1283217937605833</v>
       </c>
       <c r="W21">
-        <v>0.1269709059746804</v>
+        <v>0.1279623606759464</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.9005038158637423</v>
+        <v>0.8554786250705551</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1342701988906901</v>
+        <v>0.1352801988906902</v>
       </c>
       <c r="C22">
-        <v>1240.019608069263</v>
+        <v>1202.425283983526</v>
       </c>
       <c r="D22">
-        <v>1605.799608069263</v>
+        <v>1587.674283983526</v>
       </c>
       <c r="E22">
-        <v>340.1800000000001</v>
+        <v>359.6490000000001</v>
       </c>
       <c r="F22">
-        <v>389.3800000000001</v>
+        <v>408.849</v>
       </c>
       <c r="G22">
         <v>23.6</v>
@@ -3085,37 +3085,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M22">
-        <v>57.16098400000001</v>
+        <v>60.01903320000001</v>
       </c>
       <c r="N22">
-        <v>-8.260984000000008</v>
+        <v>-11.1190332</v>
       </c>
       <c r="O22">
-        <v>-1.239147600000001</v>
+        <v>-1.667854980000001</v>
       </c>
       <c r="P22">
-        <v>-7.021836400000007</v>
+        <v>-9.451178220000003</v>
       </c>
       <c r="Q22">
-        <v>9.278163599999994</v>
+        <v>6.848821779999998</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1358471584443761</v>
+        <v>0.1369869958930391</v>
       </c>
       <c r="T22">
-        <v>1.649245330164593</v>
+        <v>1.670121853331233</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.1283217937605833</v>
+        <v>0.1222112321529364</v>
       </c>
       <c r="W22">
-        <v>0.1279623606759464</v>
+        <v>0.1288593911199489</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8554786250705551</v>
+        <v>0.814741547686243</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1352801988906901</v>
+        <v>0.1486804828059822</v>
       </c>
       <c r="C23">
-        <v>1202.425283983526</v>
+        <v>976.1601493803341</v>
       </c>
       <c r="D23">
-        <v>1587.674283983526</v>
+        <v>1380.878149380334</v>
       </c>
       <c r="E23">
-        <v>359.649</v>
+        <v>379.1180000000001</v>
       </c>
       <c r="F23">
-        <v>408.849</v>
+        <v>428.318</v>
       </c>
       <c r="G23">
         <v>23.6</v>
@@ -3167,45 +3167,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M23">
-        <v>60.0190332</v>
+        <v>86.00625440000002</v>
       </c>
       <c r="N23">
-        <v>-11.1190332</v>
+        <v>-37.10625440000001</v>
       </c>
       <c r="O23">
-        <v>-1.66785498</v>
+        <v>-5.565938160000002</v>
       </c>
       <c r="P23">
-        <v>-9.451178219999997</v>
+        <v>-31.54031624000001</v>
       </c>
       <c r="Q23">
-        <v>6.848821780000003</v>
+        <v>-15.24031624000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1369869958930391</v>
+        <v>0.1388102700907601</v>
       </c>
       <c r="T23">
-        <v>1.670121853331233</v>
+        <v>1.703515760569944</v>
       </c>
       <c r="U23">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1222112321529365</v>
+        <v>0.08528449530991318</v>
       </c>
       <c r="W23">
-        <v>0.1288593911199489</v>
+        <v>0.1836748733417694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.814741547686243</v>
+        <v>0.5685633020660879</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1486804828059822</v>
+        <v>0.1502304828059822</v>
       </c>
       <c r="C24">
-        <v>976.1601493803341</v>
+        <v>936.195590286578</v>
       </c>
       <c r="D24">
-        <v>1380.878149380334</v>
+        <v>1360.382590286578</v>
       </c>
       <c r="E24">
-        <v>379.1180000000001</v>
+        <v>398.587</v>
       </c>
       <c r="F24">
-        <v>428.318</v>
+        <v>447.787</v>
       </c>
       <c r="G24">
         <v>23.6</v>
@@ -3249,37 +3249,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M24">
-        <v>86.00625440000002</v>
+        <v>89.91562960000002</v>
       </c>
       <c r="N24">
-        <v>-37.10625440000001</v>
+        <v>-41.01562960000001</v>
       </c>
       <c r="O24">
-        <v>-5.565938160000002</v>
+        <v>-6.152344440000001</v>
       </c>
       <c r="P24">
-        <v>-31.54031624000001</v>
+        <v>-34.86328516000001</v>
       </c>
       <c r="Q24">
-        <v>-15.24031624000001</v>
+        <v>-18.56328516000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1388102700907601</v>
+        <v>0.1400181956763544</v>
       </c>
       <c r="T24">
-        <v>1.703515760569944</v>
+        <v>1.725639341876048</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.08528449530991318</v>
+        <v>0.08157647377469955</v>
       </c>
       <c r="W24">
-        <v>0.1836748733417694</v>
+        <v>0.1844194440660403</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5685633020660879</v>
+        <v>0.543843158497997</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1502304828059822</v>
+        <v>0.1517804828059822</v>
       </c>
       <c r="C25">
-        <v>936.195590286578</v>
+        <v>896.8305400033912</v>
       </c>
       <c r="D25">
-        <v>1360.382590286578</v>
+        <v>1340.486540003391</v>
       </c>
       <c r="E25">
-        <v>398.587</v>
+        <v>418.0560000000001</v>
       </c>
       <c r="F25">
-        <v>447.787</v>
+        <v>467.2560000000001</v>
       </c>
       <c r="G25">
         <v>23.6</v>
@@ -3331,37 +3331,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M25">
-        <v>89.91562960000002</v>
+        <v>93.82500480000002</v>
       </c>
       <c r="N25">
-        <v>-41.01562960000001</v>
+        <v>-44.92500480000001</v>
       </c>
       <c r="O25">
-        <v>-6.152344440000001</v>
+        <v>-6.738750720000001</v>
       </c>
       <c r="P25">
-        <v>-34.86328516000001</v>
+        <v>-38.18625408000001</v>
       </c>
       <c r="Q25">
-        <v>-18.56328516000001</v>
+        <v>-21.88625408000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1400181956763544</v>
+        <v>0.1412579087773591</v>
       </c>
       <c r="T25">
-        <v>1.725639341876048</v>
+        <v>1.748345122690206</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.08157647377469955</v>
+        <v>0.07817745403408707</v>
       </c>
       <c r="W25">
-        <v>0.1844194440660403</v>
+        <v>0.1851019672299553</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.543843158497997</v>
+        <v>0.5211830268939139</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1517804828059822</v>
+        <v>0.1533304828059822</v>
       </c>
       <c r="C26">
-        <v>896.8305400033912</v>
+        <v>858.0390736404889</v>
       </c>
       <c r="D26">
-        <v>1340.486540003391</v>
+        <v>1321.164073640489</v>
       </c>
       <c r="E26">
-        <v>418.056</v>
+        <v>437.525</v>
       </c>
       <c r="F26">
-        <v>467.256</v>
+        <v>486.725</v>
       </c>
       <c r="G26">
         <v>23.6</v>
@@ -3413,37 +3413,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M26">
-        <v>93.8250048</v>
+        <v>97.73438</v>
       </c>
       <c r="N26">
-        <v>-44.9250048</v>
+        <v>-48.83438</v>
       </c>
       <c r="O26">
-        <v>-6.73875072</v>
+        <v>-7.325156999999999</v>
       </c>
       <c r="P26">
-        <v>-38.18625408</v>
+        <v>-41.509223</v>
       </c>
       <c r="Q26">
-        <v>-21.88625408</v>
+        <v>-25.209223</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1412579087773591</v>
+        <v>0.1425306808943905</v>
       </c>
       <c r="T26">
-        <v>1.748345122690206</v>
+        <v>1.771656390992742</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.07817745403408709</v>
+        <v>0.0750503558727236</v>
       </c>
       <c r="W26">
-        <v>0.1851019672299553</v>
+        <v>0.1857298885407571</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5211830268939139</v>
+        <v>0.5003357058181575</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1533304828059822</v>
+        <v>0.1641863885293487</v>
       </c>
       <c r="C27">
-        <v>858.0390736404889</v>
+        <v>717.4207353870931</v>
       </c>
       <c r="D27">
-        <v>1321.164073640489</v>
+        <v>1200.014735387093</v>
       </c>
       <c r="E27">
-        <v>437.525</v>
+        <v>456.994</v>
       </c>
       <c r="F27">
-        <v>486.725</v>
+        <v>506.194</v>
       </c>
       <c r="G27">
         <v>23.6</v>
@@ -3495,45 +3495,45 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M27">
-        <v>97.73438</v>
+        <v>119.3605452</v>
       </c>
       <c r="N27">
-        <v>-48.83438</v>
+        <v>-70.4605452</v>
       </c>
       <c r="O27">
-        <v>-7.325156999999999</v>
+        <v>-10.56908178</v>
       </c>
       <c r="P27">
-        <v>-41.509223</v>
+        <v>-59.89146342</v>
       </c>
       <c r="Q27">
-        <v>-25.209223</v>
+        <v>-43.59146342</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1425306808943905</v>
+        <v>0.1441161032353505</v>
       </c>
       <c r="T27">
-        <v>1.771656390992742</v>
+        <v>1.800693957944754</v>
       </c>
       <c r="U27">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.0750503558727236</v>
+        <v>0.06145246729318726</v>
       </c>
       <c r="W27">
-        <v>0.1857298885407571</v>
+        <v>0.2213095082122664</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.5003357058181575</v>
+        <v>0.4096831152879151</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1641863885293487</v>
+        <v>0.1660863885293487</v>
       </c>
       <c r="C28">
-        <v>717.4207353870931</v>
+        <v>678.9967395217113</v>
       </c>
       <c r="D28">
-        <v>1200.014735387093</v>
+        <v>1181.059739521711</v>
       </c>
       <c r="E28">
-        <v>456.994</v>
+        <v>476.463</v>
       </c>
       <c r="F28">
-        <v>506.194</v>
+        <v>525.663</v>
       </c>
       <c r="G28">
         <v>23.6</v>
@@ -3577,37 +3577,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M28">
-        <v>119.3605452</v>
+        <v>123.9513354</v>
       </c>
       <c r="N28">
-        <v>-70.4605452</v>
+        <v>-75.0513354</v>
       </c>
       <c r="O28">
-        <v>-10.56908178</v>
+        <v>-11.25770031</v>
       </c>
       <c r="P28">
-        <v>-59.89146342</v>
+        <v>-63.79363509</v>
       </c>
       <c r="Q28">
-        <v>-43.59146342</v>
+        <v>-47.49363509</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1441161032353505</v>
+        <v>0.1454628991700814</v>
       </c>
       <c r="T28">
-        <v>1.800693957944754</v>
+        <v>1.825360998464545</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.06145246729318726</v>
+        <v>0.05917644998603219</v>
       </c>
       <c r="W28">
-        <v>0.2213095082122664</v>
+        <v>0.2218461930932936</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4096831152879151</v>
+        <v>0.3945096665735479</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1660863885293487</v>
+        <v>0.1679863885293487</v>
       </c>
       <c r="C29">
-        <v>678.9967395217113</v>
+        <v>641.1622445422749</v>
       </c>
       <c r="D29">
-        <v>1181.059739521711</v>
+        <v>1162.694244542275</v>
       </c>
       <c r="E29">
-        <v>476.463</v>
+        <v>495.9320000000001</v>
       </c>
       <c r="F29">
-        <v>525.663</v>
+        <v>545.1320000000001</v>
       </c>
       <c r="G29">
         <v>23.6</v>
@@ -3659,37 +3659,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M29">
-        <v>123.9513354</v>
+        <v>128.5421256</v>
       </c>
       <c r="N29">
-        <v>-75.0513354</v>
+        <v>-79.64212560000001</v>
       </c>
       <c r="O29">
-        <v>-11.25770031</v>
+        <v>-11.94631884</v>
       </c>
       <c r="P29">
-        <v>-63.79363509</v>
+        <v>-67.69580676000001</v>
       </c>
       <c r="Q29">
-        <v>-47.49363509</v>
+        <v>-51.39580676000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1454628991700814</v>
+        <v>0.1468471061029992</v>
       </c>
       <c r="T29">
-        <v>1.825360998464545</v>
+        <v>1.85071323455433</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05917644998603219</v>
+        <v>0.05706300534367388</v>
       </c>
       <c r="W29">
-        <v>0.2218461930932936</v>
+        <v>0.2223445433399617</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3945096665735479</v>
+        <v>0.3804200356244926</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1679863885293487</v>
+        <v>0.1698863885293487</v>
       </c>
       <c r="C30">
-        <v>641.1622445422749</v>
+        <v>603.8901712897411</v>
       </c>
       <c r="D30">
-        <v>1162.694244542275</v>
+        <v>1144.891171289741</v>
       </c>
       <c r="E30">
-        <v>495.9320000000001</v>
+        <v>515.4010000000001</v>
       </c>
       <c r="F30">
-        <v>545.1320000000001</v>
+        <v>564.6010000000001</v>
       </c>
       <c r="G30">
         <v>23.6</v>
@@ -3741,37 +3741,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M30">
-        <v>128.5421256</v>
+        <v>133.1329158</v>
       </c>
       <c r="N30">
-        <v>-79.64212560000001</v>
+        <v>-84.23291580000003</v>
       </c>
       <c r="O30">
-        <v>-11.94631884</v>
+        <v>-12.63493737</v>
       </c>
       <c r="P30">
-        <v>-67.69580676000001</v>
+        <v>-71.59797843000003</v>
       </c>
       <c r="Q30">
-        <v>-51.39580676000001</v>
+        <v>-55.29797843000003</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1468471061029992</v>
+        <v>0.1482703047805062</v>
       </c>
       <c r="T30">
-        <v>1.85071323455433</v>
+        <v>1.876779618139602</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.05706300534367388</v>
+        <v>0.05509531550423685</v>
       </c>
       <c r="W30">
-        <v>0.2223445433399617</v>
+        <v>0.222808524604101</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3804200356244926</v>
+        <v>0.367302103361579</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1698863885293487</v>
+        <v>0.1717863885293487</v>
       </c>
       <c r="C31">
-        <v>603.8901712897415</v>
+        <v>567.1550741276361</v>
       </c>
       <c r="D31">
-        <v>1144.891171289742</v>
+        <v>1127.625074127636</v>
       </c>
       <c r="E31">
-        <v>515.401</v>
+        <v>534.87</v>
       </c>
       <c r="F31">
-        <v>564.601</v>
+        <v>584.0700000000001</v>
       </c>
       <c r="G31">
         <v>23.6</v>
@@ -3823,37 +3823,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M31">
-        <v>133.1329158</v>
+        <v>137.723706</v>
       </c>
       <c r="N31">
-        <v>-84.2329158</v>
+        <v>-88.82370600000002</v>
       </c>
       <c r="O31">
-        <v>-12.63493737</v>
+        <v>-13.3235559</v>
       </c>
       <c r="P31">
-        <v>-71.59797843</v>
+        <v>-75.50015010000001</v>
       </c>
       <c r="Q31">
-        <v>-55.29797843</v>
+        <v>-59.20015010000002</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1482703047805062</v>
+        <v>0.1497341662773706</v>
       </c>
       <c r="T31">
-        <v>1.876779618139602</v>
+        <v>1.903590755541597</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.05509531550423686</v>
+        <v>0.05325880498742896</v>
       </c>
       <c r="W31">
-        <v>0.222808524604101</v>
+        <v>0.2232415737839643</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3673021033615791</v>
+        <v>0.3550586999161931</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1717863885293487</v>
+        <v>0.1736863885293487</v>
       </c>
       <c r="C32">
-        <v>567.1550741276361</v>
+        <v>530.9330195963416</v>
       </c>
       <c r="D32">
-        <v>1127.625074127636</v>
+        <v>1110.872019596342</v>
       </c>
       <c r="E32">
-        <v>534.87</v>
+        <v>554.3389999999999</v>
       </c>
       <c r="F32">
-        <v>584.0700000000001</v>
+        <v>603.539</v>
       </c>
       <c r="G32">
         <v>23.6</v>
@@ -3905,37 +3905,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M32">
-        <v>137.723706</v>
+        <v>142.3144962</v>
       </c>
       <c r="N32">
-        <v>-88.82370600000002</v>
+        <v>-93.4144962</v>
       </c>
       <c r="O32">
-        <v>-13.3235559</v>
+        <v>-14.01217443</v>
       </c>
       <c r="P32">
-        <v>-75.50015010000001</v>
+        <v>-79.40232177</v>
       </c>
       <c r="Q32">
-        <v>-59.20015010000002</v>
+        <v>-63.10232177</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1497341662773706</v>
+        <v>0.15124045854226</v>
       </c>
       <c r="T32">
-        <v>1.903590755541597</v>
+        <v>1.93117902736104</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.05325880498742896</v>
+        <v>0.05154077902009254</v>
       </c>
       <c r="W32">
-        <v>0.2232415737839643</v>
+        <v>0.2236466843070622</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3550586999161931</v>
+        <v>0.3436051934672837</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1736863885293487</v>
+        <v>0.1755863885293487</v>
       </c>
       <c r="C33">
-        <v>530.9330195963416</v>
+        <v>495.2014757259897</v>
       </c>
       <c r="D33">
-        <v>1110.872019596342</v>
+        <v>1094.60947572599</v>
       </c>
       <c r="E33">
-        <v>554.3389999999999</v>
+        <v>573.808</v>
       </c>
       <c r="F33">
-        <v>603.539</v>
+        <v>623.008</v>
       </c>
       <c r="G33">
         <v>23.6</v>
@@ -3987,37 +3987,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M33">
-        <v>142.3144962</v>
+        <v>146.9052864</v>
       </c>
       <c r="N33">
-        <v>-93.4144962</v>
+        <v>-98.00528640000002</v>
       </c>
       <c r="O33">
-        <v>-14.01217443</v>
+        <v>-14.70079296</v>
       </c>
       <c r="P33">
-        <v>-79.40232177</v>
+        <v>-83.30449344000002</v>
       </c>
       <c r="Q33">
-        <v>-63.10232177</v>
+        <v>-67.00449344000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.15124045854226</v>
+        <v>0.1527910535208226</v>
       </c>
       <c r="T33">
-        <v>1.93117902736104</v>
+        <v>1.959578718939879</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.05154077902009254</v>
+        <v>0.04993012967571465</v>
       </c>
       <c r="W33">
-        <v>0.2236466843070622</v>
+        <v>0.2240264754224665</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3436051934672837</v>
+        <v>0.332867531171431</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1755863885293487</v>
+        <v>0.1774863885293487</v>
       </c>
       <c r="C34">
-        <v>495.2014757259897</v>
+        <v>459.9392109314595</v>
       </c>
       <c r="D34">
-        <v>1094.60947572599</v>
+        <v>1078.81621093146</v>
       </c>
       <c r="E34">
-        <v>573.808</v>
+        <v>593.277</v>
       </c>
       <c r="F34">
-        <v>623.008</v>
+        <v>642.4770000000001</v>
       </c>
       <c r="G34">
         <v>23.6</v>
@@ -4069,37 +4069,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M34">
-        <v>146.9052864</v>
+        <v>151.4960766</v>
       </c>
       <c r="N34">
-        <v>-98.00528640000002</v>
+        <v>-102.5960766</v>
       </c>
       <c r="O34">
-        <v>-14.70079296</v>
+        <v>-15.38941149</v>
       </c>
       <c r="P34">
-        <v>-83.30449344000002</v>
+        <v>-87.20666511000003</v>
       </c>
       <c r="Q34">
-        <v>-67.00449344000002</v>
+        <v>-70.90666511000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1527910535208226</v>
+        <v>0.1543879349166558</v>
       </c>
       <c r="T34">
-        <v>1.959578718939879</v>
+        <v>1.988826162506146</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04993012967571465</v>
+        <v>0.04841709544311722</v>
       </c>
       <c r="W34">
-        <v>0.2240264754224665</v>
+        <v>0.224383248894513</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.332867531171431</v>
+        <v>0.3227806362874482</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1774863885293487</v>
+        <v>0.1793863885293487</v>
       </c>
       <c r="C35">
-        <v>459.9392109314595</v>
+        <v>425.1262015354763</v>
       </c>
       <c r="D35">
-        <v>1078.81621093146</v>
+        <v>1063.472201535476</v>
       </c>
       <c r="E35">
-        <v>593.277</v>
+        <v>612.746</v>
       </c>
       <c r="F35">
-        <v>642.4770000000001</v>
+        <v>661.946</v>
       </c>
       <c r="G35">
         <v>23.6</v>
@@ -4151,37 +4151,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M35">
-        <v>151.4960766</v>
+        <v>156.0868668</v>
       </c>
       <c r="N35">
-        <v>-102.5960766</v>
+        <v>-107.1868668</v>
       </c>
       <c r="O35">
-        <v>-15.38941149</v>
+        <v>-16.07803002</v>
       </c>
       <c r="P35">
-        <v>-87.20666511000003</v>
+        <v>-91.10883678000002</v>
       </c>
       <c r="Q35">
-        <v>-70.90666511000003</v>
+        <v>-74.80883678000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1543879349166558</v>
+        <v>0.1560332066578173</v>
       </c>
       <c r="T35">
-        <v>1.988826162506146</v>
+        <v>2.018959892241087</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04841709544311722</v>
+        <v>0.04699306322420202</v>
       </c>
       <c r="W35">
-        <v>0.224383248894513</v>
+        <v>0.2247190356917332</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3227806362874482</v>
+        <v>0.3132870881613469</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1793863885293487</v>
+        <v>0.1812863885293487</v>
       </c>
       <c r="C36">
-        <v>425.1262015354763</v>
+        <v>390.7435470728386</v>
       </c>
       <c r="D36">
-        <v>1063.472201535476</v>
+        <v>1048.558547072839</v>
       </c>
       <c r="E36">
-        <v>612.746</v>
+        <v>632.215</v>
       </c>
       <c r="F36">
-        <v>661.946</v>
+        <v>681.4150000000001</v>
       </c>
       <c r="G36">
         <v>23.6</v>
@@ -4233,37 +4233,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M36">
-        <v>156.0868668</v>
+        <v>160.677657</v>
       </c>
       <c r="N36">
-        <v>-107.1868668</v>
+        <v>-111.777657</v>
       </c>
       <c r="O36">
-        <v>-16.07803002</v>
+        <v>-16.76664855</v>
       </c>
       <c r="P36">
-        <v>-91.10883678000002</v>
+        <v>-95.01100845000001</v>
       </c>
       <c r="Q36">
-        <v>-74.80883678000002</v>
+        <v>-78.71100845000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1560332066578173</v>
+        <v>0.1577291021448606</v>
       </c>
       <c r="T36">
-        <v>2.018959892241087</v>
+        <v>2.050020813660181</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04699306322420202</v>
+        <v>0.04565040427493911</v>
       </c>
       <c r="W36">
-        <v>0.2247190356917332</v>
+        <v>0.2250356346719694</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3132870881613469</v>
+        <v>0.3043360284995941</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1812863885293487</v>
+        <v>0.1831863885293487</v>
       </c>
       <c r="C37">
-        <v>390.7435470728386</v>
+        <v>356.773392622499</v>
       </c>
       <c r="D37">
-        <v>1048.558547072839</v>
+        <v>1034.057392622499</v>
       </c>
       <c r="E37">
-        <v>632.215</v>
+        <v>651.6840000000001</v>
       </c>
       <c r="F37">
-        <v>681.4150000000001</v>
+        <v>700.8840000000001</v>
       </c>
       <c r="G37">
         <v>23.6</v>
@@ -4315,37 +4315,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M37">
-        <v>160.677657</v>
+        <v>165.2684472</v>
       </c>
       <c r="N37">
-        <v>-111.777657</v>
+        <v>-116.3684472</v>
       </c>
       <c r="O37">
-        <v>-16.76664855</v>
+        <v>-17.45526708</v>
       </c>
       <c r="P37">
-        <v>-95.01100845000001</v>
+        <v>-98.91318012000002</v>
       </c>
       <c r="Q37">
-        <v>-78.71100845000001</v>
+        <v>-82.61318012000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1577291021448606</v>
+        <v>0.1594779943658741</v>
       </c>
       <c r="T37">
-        <v>2.050020813660181</v>
+        <v>2.082052388873621</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04565040427493911</v>
+        <v>0.04438233748952413</v>
       </c>
       <c r="W37">
-        <v>0.2250356346719694</v>
+        <v>0.2253346448199702</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3043360284995941</v>
+        <v>0.2958822499301609</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1831863885293487</v>
+        <v>0.1850863885293487</v>
       </c>
       <c r="C38">
-        <v>356.7733926224992</v>
+        <v>323.1988574964396</v>
       </c>
       <c r="D38">
-        <v>1034.057392622499</v>
+        <v>1019.95185749644</v>
       </c>
       <c r="E38">
-        <v>651.684</v>
+        <v>671.153</v>
       </c>
       <c r="F38">
-        <v>700.884</v>
+        <v>720.3530000000001</v>
       </c>
       <c r="G38">
         <v>23.6</v>
@@ -4397,37 +4397,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M38">
-        <v>165.2684472</v>
+        <v>169.8592374</v>
       </c>
       <c r="N38">
-        <v>-116.3684472</v>
+        <v>-120.9592374</v>
       </c>
       <c r="O38">
-        <v>-17.45526708</v>
+        <v>-18.14388561</v>
       </c>
       <c r="P38">
-        <v>-98.91318011999999</v>
+        <v>-102.81535179</v>
       </c>
       <c r="Q38">
-        <v>-82.61318012</v>
+        <v>-86.51535179000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1594779943658741</v>
+        <v>0.1612824069748562</v>
       </c>
       <c r="T38">
-        <v>2.082052388873621</v>
+        <v>2.115100839490663</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04438233748952414</v>
+        <v>0.04318281485467213</v>
       </c>
       <c r="W38">
-        <v>0.2253346448199702</v>
+        <v>0.2256174922572683</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.295882249930161</v>
+        <v>0.2878854323644808</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1850863885293487</v>
+        <v>0.1869863885293487</v>
       </c>
       <c r="C39">
-        <v>323.1988574964396</v>
+        <v>290.003969686508</v>
       </c>
       <c r="D39">
-        <v>1019.95185749644</v>
+        <v>1006.225969686508</v>
       </c>
       <c r="E39">
-        <v>671.153</v>
+        <v>690.622</v>
       </c>
       <c r="F39">
-        <v>720.3530000000001</v>
+        <v>739.822</v>
       </c>
       <c r="G39">
         <v>23.6</v>
@@ -4479,37 +4479,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M39">
-        <v>169.8592374</v>
+        <v>174.4500276</v>
       </c>
       <c r="N39">
-        <v>-120.9592374</v>
+        <v>-125.5500276</v>
       </c>
       <c r="O39">
-        <v>-18.14388561</v>
+        <v>-18.83250414</v>
       </c>
       <c r="P39">
-        <v>-102.81535179</v>
+        <v>-106.71752346</v>
       </c>
       <c r="Q39">
-        <v>-86.51535179000001</v>
+        <v>-90.41752346</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1612824069748562</v>
+        <v>0.1631450264421926</v>
       </c>
       <c r="T39">
-        <v>2.115100839490663</v>
+        <v>2.149215369159867</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04318281485467213</v>
+        <v>0.0420464249900755</v>
       </c>
       <c r="W39">
-        <v>0.2256174922572683</v>
+        <v>0.2258854529873402</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2878854323644808</v>
+        <v>0.2803094999338367</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1869863885293487</v>
+        <v>0.1888863885293487</v>
       </c>
       <c r="C40">
-        <v>290.003969686508</v>
+        <v>257.1736055340245</v>
       </c>
       <c r="D40">
-        <v>1006.225969686508</v>
+        <v>992.8646055340246</v>
       </c>
       <c r="E40">
-        <v>690.622</v>
+        <v>710.091</v>
       </c>
       <c r="F40">
-        <v>739.822</v>
+        <v>759.2910000000001</v>
       </c>
       <c r="G40">
         <v>23.6</v>
@@ -4561,37 +4561,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M40">
-        <v>174.4500276</v>
+        <v>179.0408178</v>
       </c>
       <c r="N40">
-        <v>-125.5500276</v>
+        <v>-130.1408178</v>
       </c>
       <c r="O40">
-        <v>-18.83250414</v>
+        <v>-19.52112267</v>
       </c>
       <c r="P40">
-        <v>-106.71752346</v>
+        <v>-110.61969513</v>
       </c>
       <c r="Q40">
-        <v>-90.41752346</v>
+        <v>-94.31969513000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1631450264421926</v>
+        <v>0.1650687154002613</v>
       </c>
       <c r="T40">
-        <v>2.149215369159867</v>
+        <v>2.184448407998554</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.0420464249900755</v>
+        <v>0.04096831152879151</v>
       </c>
       <c r="W40">
-        <v>0.2258854529873402</v>
+        <v>0.226139672141511</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2803094999338367</v>
+        <v>0.2731220768586101</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1888863885293487</v>
+        <v>0.1907863885293487</v>
       </c>
       <c r="C41">
-        <v>257.1736055340245</v>
+        <v>224.693434143044</v>
       </c>
       <c r="D41">
-        <v>992.8646055340246</v>
+        <v>979.8534341430441</v>
       </c>
       <c r="E41">
-        <v>710.091</v>
+        <v>729.5600000000001</v>
       </c>
       <c r="F41">
-        <v>759.2910000000001</v>
+        <v>778.7600000000001</v>
       </c>
       <c r="G41">
         <v>23.6</v>
@@ -4643,37 +4643,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M41">
-        <v>179.0408178</v>
+        <v>183.631608</v>
       </c>
       <c r="N41">
-        <v>-130.1408178</v>
+        <v>-134.731608</v>
       </c>
       <c r="O41">
-        <v>-19.52112267</v>
+        <v>-20.2097412</v>
       </c>
       <c r="P41">
-        <v>-110.61969513</v>
+        <v>-114.5218668</v>
       </c>
       <c r="Q41">
-        <v>-94.31969513000001</v>
+        <v>-98.22186680000003</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1650687154002613</v>
+        <v>0.167056527323599</v>
       </c>
       <c r="T41">
-        <v>2.184448407998554</v>
+        <v>2.220855881465196</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04096831152879151</v>
+        <v>0.03994410374057172</v>
       </c>
       <c r="W41">
-        <v>0.226139672141511</v>
+        <v>0.2263811803379732</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2731220768586101</v>
+        <v>0.2662940249371448</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1907863885293487</v>
+        <v>0.1926863885293487</v>
       </c>
       <c r="C42">
-        <v>224.693434143044</v>
+        <v>192.5498661077645</v>
       </c>
       <c r="D42">
-        <v>979.8534341430441</v>
+        <v>967.1788661077645</v>
       </c>
       <c r="E42">
-        <v>729.5600000000001</v>
+        <v>749.029</v>
       </c>
       <c r="F42">
-        <v>778.7600000000001</v>
+        <v>798.229</v>
       </c>
       <c r="G42">
         <v>23.6</v>
@@ -4725,37 +4725,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M42">
-        <v>183.631608</v>
+        <v>188.2223982</v>
       </c>
       <c r="N42">
-        <v>-134.731608</v>
+        <v>-139.3223982</v>
       </c>
       <c r="O42">
-        <v>-20.2097412</v>
+        <v>-20.89835973</v>
       </c>
       <c r="P42">
-        <v>-114.5218668</v>
+        <v>-118.42403847</v>
       </c>
       <c r="Q42">
-        <v>-98.22186680000003</v>
+        <v>-102.12403847</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.167056527323599</v>
+        <v>0.1691117227019651</v>
       </c>
       <c r="T42">
-        <v>2.220855881465196</v>
+        <v>2.258497506574776</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03994410374057172</v>
+        <v>0.03896985730787485</v>
       </c>
       <c r="W42">
-        <v>0.2263811803379732</v>
+        <v>0.2266109076468031</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2662940249371448</v>
+        <v>0.2597990487191657</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1926863885293487</v>
+        <v>0.1945863885293487</v>
       </c>
       <c r="C43">
-        <v>192.5498661077645</v>
+        <v>160.730006168434</v>
       </c>
       <c r="D43">
-        <v>967.1788661077645</v>
+        <v>954.8280061684341</v>
       </c>
       <c r="E43">
-        <v>749.029</v>
+        <v>768.498</v>
       </c>
       <c r="F43">
-        <v>798.229</v>
+        <v>817.6980000000001</v>
       </c>
       <c r="G43">
         <v>23.6</v>
@@ -4807,37 +4807,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M43">
-        <v>188.2223982</v>
+        <v>192.8131884</v>
       </c>
       <c r="N43">
-        <v>-139.3223982</v>
+        <v>-143.9131884</v>
       </c>
       <c r="O43">
-        <v>-20.89835973</v>
+        <v>-21.58697826</v>
       </c>
       <c r="P43">
-        <v>-118.42403847</v>
+        <v>-122.32621014</v>
       </c>
       <c r="Q43">
-        <v>-102.12403847</v>
+        <v>-106.02621014</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1691117227019651</v>
+        <v>0.1712377868864817</v>
       </c>
       <c r="T43">
-        <v>2.258497506574776</v>
+        <v>2.297437118757099</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03896985730787485</v>
+        <v>0.03804200356244925</v>
       </c>
       <c r="W43">
-        <v>0.2266109076468031</v>
+        <v>0.2268296955599745</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2597990487191657</v>
+        <v>0.253613357082995</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1945863885293487</v>
+        <v>0.1964863885293487</v>
       </c>
       <c r="C44">
-        <v>160.7300061684341</v>
+        <v>129.2216094490236</v>
       </c>
       <c r="D44">
-        <v>954.8280061684341</v>
+        <v>942.7886094490236</v>
       </c>
       <c r="E44">
-        <v>768.4979999999999</v>
+        <v>787.967</v>
       </c>
       <c r="F44">
-        <v>817.698</v>
+        <v>837.167</v>
       </c>
       <c r="G44">
         <v>23.6</v>
@@ -4889,37 +4889,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M44">
-        <v>192.8131884</v>
+        <v>197.4039786</v>
       </c>
       <c r="N44">
-        <v>-143.9131884</v>
+        <v>-148.5039786</v>
       </c>
       <c r="O44">
-        <v>-21.58697826</v>
+        <v>-22.27559679</v>
       </c>
       <c r="P44">
-        <v>-122.32621014</v>
+        <v>-126.22838181</v>
       </c>
       <c r="Q44">
-        <v>-106.02621014</v>
+        <v>-109.92838181</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1712377868864817</v>
+        <v>0.1734384498143147</v>
       </c>
       <c r="T44">
-        <v>2.297437118757099</v>
+        <v>2.337743033121259</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03804200356244927</v>
+        <v>0.037157305805183</v>
       </c>
       <c r="W44">
-        <v>0.2268296955599745</v>
+        <v>0.2270383072911379</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.253613357082995</v>
+        <v>0.2477153720345533</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1964863885293487</v>
+        <v>0.1983863885293487</v>
       </c>
       <c r="C45">
-        <v>129.2216094490236</v>
+        <v>98.01304096445597</v>
       </c>
       <c r="D45">
-        <v>942.7886094490236</v>
+        <v>931.049040964456</v>
       </c>
       <c r="E45">
-        <v>787.967</v>
+        <v>807.436</v>
       </c>
       <c r="F45">
-        <v>837.167</v>
+        <v>856.6360000000001</v>
       </c>
       <c r="G45">
         <v>23.6</v>
@@ -4971,37 +4971,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M45">
-        <v>197.4039786</v>
+        <v>201.9947688</v>
       </c>
       <c r="N45">
-        <v>-148.5039786</v>
+        <v>-153.0947688</v>
       </c>
       <c r="O45">
-        <v>-22.27559679</v>
+        <v>-22.96421532</v>
       </c>
       <c r="P45">
-        <v>-126.22838181</v>
+        <v>-130.13055348</v>
       </c>
       <c r="Q45">
-        <v>-109.92838181</v>
+        <v>-113.83055348</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1734384498143147</v>
+        <v>0.1757177078467132</v>
       </c>
       <c r="T45">
-        <v>2.337743033121259</v>
+        <v>2.379488444426996</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.037157305805183</v>
+        <v>0.03631282158233792</v>
       </c>
       <c r="W45">
-        <v>0.2270383072911379</v>
+        <v>0.2272374366708847</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2477153720345533</v>
+        <v>0.2420854772155862</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1983863885293487</v>
+        <v>0.2002863885293487</v>
       </c>
       <c r="C46">
-        <v>98.01304096445597</v>
+        <v>67.09323811591639</v>
       </c>
       <c r="D46">
-        <v>931.049040964456</v>
+        <v>919.5982381159164</v>
       </c>
       <c r="E46">
-        <v>807.436</v>
+        <v>826.905</v>
       </c>
       <c r="F46">
-        <v>856.6360000000001</v>
+        <v>876.105</v>
       </c>
       <c r="G46">
         <v>23.6</v>
@@ -5053,37 +5053,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M46">
-        <v>201.9947688</v>
+        <v>206.585559</v>
       </c>
       <c r="N46">
-        <v>-153.0947688</v>
+        <v>-157.685559</v>
       </c>
       <c r="O46">
-        <v>-22.96421532</v>
+        <v>-23.65283385</v>
       </c>
       <c r="P46">
-        <v>-130.13055348</v>
+        <v>-134.03272515</v>
       </c>
       <c r="Q46">
-        <v>-113.83055348</v>
+        <v>-117.73272515</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1757177078467132</v>
+        <v>0.1780798479893807</v>
       </c>
       <c r="T46">
-        <v>2.379488444426996</v>
+        <v>2.422751870689305</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03631282158233792</v>
+        <v>0.0355058699916193</v>
       </c>
       <c r="W46">
-        <v>0.2272374366708847</v>
+        <v>0.2274277158559762</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2420854772155862</v>
+        <v>0.2367057999441288</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2002863885293487</v>
+        <v>0.2021863885293487</v>
       </c>
       <c r="C47">
-        <v>67.09323811591639</v>
+        <v>36.45167592011899</v>
       </c>
       <c r="D47">
-        <v>919.5982381159164</v>
+        <v>908.425675920119</v>
       </c>
       <c r="E47">
-        <v>826.905</v>
+        <v>846.374</v>
       </c>
       <c r="F47">
-        <v>876.105</v>
+        <v>895.5740000000001</v>
       </c>
       <c r="G47">
         <v>23.6</v>
@@ -5135,37 +5135,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M47">
-        <v>206.585559</v>
+        <v>211.1763492</v>
       </c>
       <c r="N47">
-        <v>-157.685559</v>
+        <v>-162.2763492</v>
       </c>
       <c r="O47">
-        <v>-23.65283385</v>
+        <v>-24.34145238</v>
       </c>
       <c r="P47">
-        <v>-134.03272515</v>
+        <v>-137.93489682</v>
       </c>
       <c r="Q47">
-        <v>-117.73272515</v>
+        <v>-121.63489682</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1780798479893807</v>
+        <v>0.1805294748039989</v>
       </c>
       <c r="T47">
-        <v>2.422751870689305</v>
+        <v>2.46761764607244</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0355058699916193</v>
+        <v>0.03473400325267106</v>
       </c>
       <c r="W47">
-        <v>0.2274277158559762</v>
+        <v>0.2276097220330202</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2367057999441288</v>
+        <v>0.2315600216844738</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2021863885293487</v>
+        <v>0.2040863885293487</v>
       </c>
       <c r="C48">
-        <v>36.45167592011899</v>
+        <v>6.078334742809488</v>
       </c>
       <c r="D48">
-        <v>908.425675920119</v>
+        <v>897.5213347428096</v>
       </c>
       <c r="E48">
-        <v>846.374</v>
+        <v>865.8430000000001</v>
       </c>
       <c r="F48">
-        <v>895.5740000000001</v>
+        <v>915.0430000000001</v>
       </c>
       <c r="G48">
         <v>23.6</v>
@@ -5217,37 +5217,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M48">
-        <v>211.1763492</v>
+        <v>215.7671394</v>
       </c>
       <c r="N48">
-        <v>-162.2763492</v>
+        <v>-166.8671394</v>
       </c>
       <c r="O48">
-        <v>-24.34145238</v>
+        <v>-25.03007091000001</v>
       </c>
       <c r="P48">
-        <v>-137.93489682</v>
+        <v>-141.83706849</v>
       </c>
       <c r="Q48">
-        <v>-121.63489682</v>
+        <v>-125.53706849</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1805294748039989</v>
+        <v>0.1830715403663385</v>
       </c>
       <c r="T48">
-        <v>2.46761764607244</v>
+        <v>2.514176469583241</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03473400325267106</v>
+        <v>0.03399498190686955</v>
       </c>
       <c r="W48">
-        <v>0.2276097220330202</v>
+        <v>0.2277839832663602</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2315600216844738</v>
+        <v>0.2266332127124636</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2040863885293487</v>
+        <v>0.2059863885293487</v>
       </c>
       <c r="C49">
-        <v>6.078334742809488</v>
+        <v>-24.03632967142335</v>
       </c>
       <c r="D49">
-        <v>897.5213347428096</v>
+        <v>886.8756703285768</v>
       </c>
       <c r="E49">
-        <v>865.8430000000001</v>
+        <v>885.3120000000001</v>
       </c>
       <c r="F49">
-        <v>915.0430000000001</v>
+        <v>934.5120000000002</v>
       </c>
       <c r="G49">
         <v>23.6</v>
@@ -5299,37 +5299,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M49">
-        <v>215.7671394</v>
+        <v>220.3579296000001</v>
       </c>
       <c r="N49">
-        <v>-166.8671394</v>
+        <v>-171.4579296000001</v>
       </c>
       <c r="O49">
-        <v>-25.03007091000001</v>
+        <v>-25.71868944000001</v>
       </c>
       <c r="P49">
-        <v>-141.83706849</v>
+        <v>-145.73924016</v>
       </c>
       <c r="Q49">
-        <v>-125.53706849</v>
+        <v>-129.43924016</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1830715403663385</v>
+        <v>0.1857113776810758</v>
       </c>
       <c r="T49">
-        <v>2.514176469583241</v>
+        <v>2.562526017075226</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03399498190686955</v>
+        <v>0.0332867531171431</v>
       </c>
       <c r="W49">
-        <v>0.2277839832663602</v>
+        <v>0.2279509836149776</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2266332127124636</v>
+        <v>0.2219116874476207</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2059863885293487</v>
+        <v>0.2078863885293487</v>
       </c>
       <c r="C50">
-        <v>-24.03632967142323</v>
+        <v>-53.90141406144085</v>
       </c>
       <c r="D50">
-        <v>886.8756703285768</v>
+        <v>876.4795859385591</v>
       </c>
       <c r="E50">
-        <v>885.312</v>
+        <v>904.7809999999999</v>
       </c>
       <c r="F50">
-        <v>934.5120000000001</v>
+        <v>953.981</v>
       </c>
       <c r="G50">
         <v>23.6</v>
@@ -5381,37 +5381,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M50">
-        <v>220.3579296</v>
+        <v>224.9487198</v>
       </c>
       <c r="N50">
-        <v>-171.4579296</v>
+        <v>-176.0487198</v>
       </c>
       <c r="O50">
-        <v>-25.71868944</v>
+        <v>-26.40730797</v>
       </c>
       <c r="P50">
-        <v>-145.73924016</v>
+        <v>-149.64141183</v>
       </c>
       <c r="Q50">
-        <v>-129.43924016</v>
+        <v>-133.34141183</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1857113776810758</v>
+        <v>0.1884547380277635</v>
       </c>
       <c r="T50">
-        <v>2.562526017075226</v>
+        <v>2.612771625253171</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0332867531171431</v>
+        <v>0.03260743162495651</v>
       </c>
       <c r="W50">
-        <v>0.2279509836149776</v>
+        <v>0.2281111676228353</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2219116874476207</v>
+        <v>0.2173828774997101</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2078863885293487</v>
+        <v>0.2097863885293487</v>
       </c>
       <c r="C51">
-        <v>-53.90141406144085</v>
+        <v>-83.52559357492339</v>
       </c>
       <c r="D51">
-        <v>876.4795859385591</v>
+        <v>866.3244064250766</v>
       </c>
       <c r="E51">
-        <v>904.7809999999999</v>
+        <v>924.25</v>
       </c>
       <c r="F51">
-        <v>953.981</v>
+        <v>973.45</v>
       </c>
       <c r="G51">
         <v>23.6</v>
@@ -5463,37 +5463,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M51">
-        <v>224.9487198</v>
+        <v>229.53951</v>
       </c>
       <c r="N51">
-        <v>-176.0487198</v>
+        <v>-180.63951</v>
       </c>
       <c r="O51">
-        <v>-26.40730797</v>
+        <v>-27.0959265</v>
       </c>
       <c r="P51">
-        <v>-149.64141183</v>
+        <v>-153.5435835</v>
       </c>
       <c r="Q51">
-        <v>-133.34141183</v>
+        <v>-137.2435835</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1884547380277635</v>
+        <v>0.1913078327883188</v>
       </c>
       <c r="T51">
-        <v>2.612771625253171</v>
+        <v>2.665027057758235</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03260743162495651</v>
+        <v>0.03195528299245737</v>
       </c>
       <c r="W51">
-        <v>0.2281111676228353</v>
+        <v>0.2282649442703786</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2173828774997101</v>
+        <v>0.2130352199497159</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2097863885293487</v>
+        <v>0.2116863885293487</v>
       </c>
       <c r="C52">
-        <v>-83.52559357492339</v>
+        <v>-112.9171459121</v>
       </c>
       <c r="D52">
-        <v>866.3244064250766</v>
+        <v>856.4018540879001</v>
       </c>
       <c r="E52">
-        <v>924.25</v>
+        <v>943.7190000000001</v>
       </c>
       <c r="F52">
-        <v>973.45</v>
+        <v>992.9190000000001</v>
       </c>
       <c r="G52">
         <v>23.6</v>
@@ -5545,37 +5545,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M52">
-        <v>229.53951</v>
+        <v>234.1303002</v>
       </c>
       <c r="N52">
-        <v>-180.63951</v>
+        <v>-185.2303002</v>
       </c>
       <c r="O52">
-        <v>-27.0959265</v>
+        <v>-27.78454503</v>
       </c>
       <c r="P52">
-        <v>-153.5435835</v>
+        <v>-157.44575517</v>
       </c>
       <c r="Q52">
-        <v>-137.2435835</v>
+        <v>-141.14575517</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1913078327883188</v>
+        <v>0.1942773803962437</v>
       </c>
       <c r="T52">
-        <v>2.665027057758235</v>
+        <v>2.719415365059424</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03195528299245737</v>
+        <v>0.03132870881613468</v>
       </c>
       <c r="W52">
-        <v>0.2282649442703786</v>
+        <v>0.2284126904611554</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2130352199497159</v>
+        <v>0.2088580587742312</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2116863885293487</v>
+        <v>0.2135863885293487</v>
       </c>
       <c r="C53">
-        <v>-112.9171459121</v>
+        <v>-142.083973829067</v>
       </c>
       <c r="D53">
-        <v>856.4018540879001</v>
+        <v>846.704026170933</v>
       </c>
       <c r="E53">
-        <v>943.7190000000001</v>
+        <v>963.188</v>
       </c>
       <c r="F53">
-        <v>992.9190000000001</v>
+        <v>1012.388</v>
       </c>
       <c r="G53">
         <v>23.6</v>
@@ -5627,37 +5627,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M53">
-        <v>234.1303002</v>
+        <v>238.7210904</v>
       </c>
       <c r="N53">
-        <v>-185.2303002</v>
+        <v>-189.8210904</v>
       </c>
       <c r="O53">
-        <v>-27.78454503</v>
+        <v>-28.47316356</v>
       </c>
       <c r="P53">
-        <v>-157.44575517</v>
+        <v>-161.34792684</v>
       </c>
       <c r="Q53">
-        <v>-141.14575517</v>
+        <v>-145.04792684</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1942773803962437</v>
+        <v>0.1973706591544988</v>
       </c>
       <c r="T53">
-        <v>2.719415365059424</v>
+        <v>2.776069851831495</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03132870881613468</v>
+        <v>0.03072623364659363</v>
       </c>
       <c r="W53">
-        <v>0.2284126904611554</v>
+        <v>0.2285547541061332</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2088580587742312</v>
+        <v>0.2048415576439575</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2135863885293487</v>
+        <v>0.2154863885293487</v>
       </c>
       <c r="C54">
-        <v>-142.083973829067</v>
+        <v>-171.0336261292755</v>
       </c>
       <c r="D54">
-        <v>846.704026170933</v>
+        <v>837.2233738707247</v>
       </c>
       <c r="E54">
-        <v>963.188</v>
+        <v>982.6570000000002</v>
       </c>
       <c r="F54">
-        <v>1012.388</v>
+        <v>1031.857</v>
       </c>
       <c r="G54">
         <v>23.6</v>
@@ -5709,37 +5709,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M54">
-        <v>238.7210904</v>
+        <v>243.3118806000001</v>
       </c>
       <c r="N54">
-        <v>-189.8210904</v>
+        <v>-194.4118806</v>
       </c>
       <c r="O54">
-        <v>-28.47316356</v>
+        <v>-29.16178209000001</v>
       </c>
       <c r="P54">
-        <v>-161.34792684</v>
+        <v>-165.25009851</v>
       </c>
       <c r="Q54">
-        <v>-145.04792684</v>
+        <v>-148.95009851</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1973706591544988</v>
+        <v>0.2005955667960838</v>
       </c>
       <c r="T54">
-        <v>2.776069851831495</v>
+        <v>2.83513516782791</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03072623364659363</v>
+        <v>0.03014649338911073</v>
       </c>
       <c r="W54">
-        <v>0.2285547541061332</v>
+        <v>0.2286914568588477</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2048415576439575</v>
+        <v>0.2009766225940716</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2154863885293487</v>
+        <v>0.2173863885293487</v>
       </c>
       <c r="C55">
-        <v>-171.0336261292755</v>
+        <v>-199.7733172603629</v>
       </c>
       <c r="D55">
-        <v>837.2233738707247</v>
+        <v>827.9526827396371</v>
       </c>
       <c r="E55">
-        <v>982.6570000000002</v>
+        <v>1002.126</v>
       </c>
       <c r="F55">
-        <v>1031.857</v>
+        <v>1051.326</v>
       </c>
       <c r="G55">
         <v>23.6</v>
@@ -5791,37 +5791,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M55">
-        <v>243.3118806000001</v>
+        <v>247.9026708</v>
       </c>
       <c r="N55">
-        <v>-194.4118806</v>
+        <v>-199.0026708</v>
       </c>
       <c r="O55">
-        <v>-29.16178209000001</v>
+        <v>-29.85040062</v>
       </c>
       <c r="P55">
-        <v>-165.25009851</v>
+        <v>-169.15227018</v>
       </c>
       <c r="Q55">
-        <v>-148.95009851</v>
+        <v>-152.85227018</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2005955667960838</v>
+        <v>0.20396068781339</v>
       </c>
       <c r="T55">
-        <v>2.83513516782791</v>
+        <v>2.89676854104156</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03014649338911073</v>
+        <v>0.02958822499301609</v>
       </c>
       <c r="W55">
-        <v>0.2286914568588477</v>
+        <v>0.2288230965466468</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2009766225940716</v>
+        <v>0.197254833286774</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2173863885293487</v>
+        <v>0.2192863885293487</v>
       </c>
       <c r="C56">
-        <v>-199.7733172603629</v>
+        <v>-228.3099456232599</v>
       </c>
       <c r="D56">
-        <v>827.9526827396371</v>
+        <v>818.8850543767402</v>
       </c>
       <c r="E56">
-        <v>1002.126</v>
+        <v>1021.595</v>
       </c>
       <c r="F56">
-        <v>1051.326</v>
+        <v>1070.795</v>
       </c>
       <c r="G56">
         <v>23.6</v>
@@ -5873,37 +5873,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M56">
-        <v>247.9026708</v>
+        <v>252.493461</v>
       </c>
       <c r="N56">
-        <v>-199.0026708</v>
+        <v>-203.593461</v>
       </c>
       <c r="O56">
-        <v>-29.85040062</v>
+        <v>-30.53901915</v>
       </c>
       <c r="P56">
-        <v>-169.15227018</v>
+        <v>-173.05444185</v>
       </c>
       <c r="Q56">
-        <v>-152.85227018</v>
+        <v>-156.75444185</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.20396068781339</v>
+        <v>0.2074753697647987</v>
       </c>
       <c r="T56">
-        <v>2.89676854104156</v>
+        <v>2.961141175286929</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02958822499301609</v>
+        <v>0.02905025726587034</v>
       </c>
       <c r="W56">
-        <v>0.2288230965466468</v>
+        <v>0.2289499493367078</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.197254833286774</v>
+        <v>0.1936683817724689</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2192863885293487</v>
+        <v>0.2211863885293487</v>
       </c>
       <c r="C57">
-        <v>-228.3099456232599</v>
+        <v>-256.6501106912121</v>
       </c>
       <c r="D57">
-        <v>818.8850543767402</v>
+        <v>810.013889308788</v>
       </c>
       <c r="E57">
-        <v>1021.595</v>
+        <v>1041.064</v>
       </c>
       <c r="F57">
-        <v>1070.795</v>
+        <v>1090.264</v>
       </c>
       <c r="G57">
         <v>23.6</v>
@@ -5955,37 +5955,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M57">
-        <v>252.493461</v>
+        <v>257.0842512</v>
       </c>
       <c r="N57">
-        <v>-203.593461</v>
+        <v>-208.1842512</v>
       </c>
       <c r="O57">
-        <v>-30.53901915</v>
+        <v>-31.22763768</v>
       </c>
       <c r="P57">
-        <v>-173.05444185</v>
+        <v>-176.95661352</v>
       </c>
       <c r="Q57">
-        <v>-156.75444185</v>
+        <v>-160.65661352</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2074753697647987</v>
+        <v>0.2111498099867259</v>
       </c>
       <c r="T57">
-        <v>2.961141175286929</v>
+        <v>3.028439838361631</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02905025726587034</v>
+        <v>0.02853150267183694</v>
       </c>
       <c r="W57">
-        <v>0.2289499493367078</v>
+        <v>0.2290722716699809</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1936683817724689</v>
+        <v>0.1902100178122463</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2211863885293487</v>
+        <v>0.2230863885293487</v>
       </c>
       <c r="C58">
-        <v>-256.6501106912121</v>
+        <v>-284.8001290280027</v>
       </c>
       <c r="D58">
-        <v>810.013889308788</v>
+        <v>801.3328709719974</v>
       </c>
       <c r="E58">
-        <v>1041.064</v>
+        <v>1060.533</v>
       </c>
       <c r="F58">
-        <v>1090.264</v>
+        <v>1109.733</v>
       </c>
       <c r="G58">
         <v>23.6</v>
@@ -6037,37 +6037,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M58">
-        <v>257.0842512</v>
+        <v>261.6750414000001</v>
       </c>
       <c r="N58">
-        <v>-208.1842512</v>
+        <v>-212.7750414</v>
       </c>
       <c r="O58">
-        <v>-31.22763768</v>
+        <v>-31.91625621000001</v>
       </c>
       <c r="P58">
-        <v>-176.95661352</v>
+        <v>-180.85878519</v>
       </c>
       <c r="Q58">
-        <v>-160.65661352</v>
+        <v>-164.55878519</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2111498099867259</v>
+        <v>0.2149951544050219</v>
       </c>
       <c r="T58">
-        <v>3.028439838361631</v>
+        <v>3.098868671811902</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02853150267183694</v>
+        <v>0.02803094999338366</v>
       </c>
       <c r="W58">
-        <v>0.2290722716699809</v>
+        <v>0.2291903019915602</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1902100178122463</v>
+        <v>0.1868729999558911</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2230863885293487</v>
+        <v>0.2249863885293487</v>
       </c>
       <c r="C59">
-        <v>-284.8001290280027</v>
+        <v>-312.766049287085</v>
       </c>
       <c r="D59">
-        <v>801.3328709719974</v>
+        <v>792.8359507129152</v>
       </c>
       <c r="E59">
-        <v>1060.533</v>
+        <v>1080.002</v>
       </c>
       <c r="F59">
-        <v>1109.733</v>
+        <v>1129.202</v>
       </c>
       <c r="G59">
         <v>23.6</v>
@@ -6119,37 +6119,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M59">
-        <v>261.6750414000001</v>
+        <v>266.2658316000001</v>
       </c>
       <c r="N59">
-        <v>-212.7750414</v>
+        <v>-217.3658316000001</v>
       </c>
       <c r="O59">
-        <v>-31.91625621000001</v>
+        <v>-32.60487474000001</v>
       </c>
       <c r="P59">
-        <v>-180.85878519</v>
+        <v>-184.7609568600001</v>
       </c>
       <c r="Q59">
-        <v>-164.55878519</v>
+        <v>-168.46095686</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2149951544050219</v>
+        <v>0.2190236104622843</v>
       </c>
       <c r="T59">
-        <v>3.098868671811902</v>
+        <v>3.172651259235995</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02803094999338366</v>
+        <v>0.02754765775211842</v>
       </c>
       <c r="W59">
-        <v>0.2291903019915602</v>
+        <v>0.2293042623020505</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1868729999558911</v>
+        <v>0.1836510516807895</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2249863885293487</v>
+        <v>0.2268863885293487</v>
       </c>
       <c r="C60">
-        <v>-312.766049287085</v>
+        <v>-340.5536662664632</v>
       </c>
       <c r="D60">
-        <v>792.835950712915</v>
+        <v>784.5173337335368</v>
       </c>
       <c r="E60">
-        <v>1080.002</v>
+        <v>1099.471</v>
       </c>
       <c r="F60">
-        <v>1129.202</v>
+        <v>1148.671</v>
       </c>
       <c r="G60">
         <v>23.6</v>
@@ -6201,37 +6201,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M60">
-        <v>266.2658316</v>
+        <v>270.8566218</v>
       </c>
       <c r="N60">
-        <v>-217.3658316</v>
+        <v>-221.9566218</v>
       </c>
       <c r="O60">
-        <v>-32.60487474</v>
+        <v>-33.29349327</v>
       </c>
       <c r="P60">
-        <v>-184.76095686</v>
+        <v>-188.66312853</v>
       </c>
       <c r="Q60">
-        <v>-168.46095686</v>
+        <v>-172.36312853</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2190236104622843</v>
+        <v>0.2232485765711205</v>
       </c>
       <c r="T60">
-        <v>3.172651259235994</v>
+        <v>3.25003299726614</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02754765775211843</v>
+        <v>0.02708074829869269</v>
       </c>
       <c r="W60">
-        <v>0.2293042623020505</v>
+        <v>0.2294143595511683</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1836510516807895</v>
+        <v>0.1805383219912846</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2268863885293487</v>
+        <v>0.2287863885293487</v>
       </c>
       <c r="C61">
-        <v>-340.5536662664632</v>
+        <v>-368.1685340879633</v>
       </c>
       <c r="D61">
-        <v>784.5173337335368</v>
+        <v>776.3714659120368</v>
       </c>
       <c r="E61">
-        <v>1099.471</v>
+        <v>1118.94</v>
       </c>
       <c r="F61">
-        <v>1148.671</v>
+        <v>1168.14</v>
       </c>
       <c r="G61">
         <v>23.6</v>
@@ -6283,37 +6283,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M61">
-        <v>270.8566218</v>
+        <v>275.447412</v>
       </c>
       <c r="N61">
-        <v>-221.9566218</v>
+        <v>-226.547412</v>
       </c>
       <c r="O61">
-        <v>-33.29349327</v>
+        <v>-33.98211180000001</v>
       </c>
       <c r="P61">
-        <v>-188.66312853</v>
+        <v>-192.5653002</v>
       </c>
       <c r="Q61">
-        <v>-172.36312853</v>
+        <v>-176.2653002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2232485765711205</v>
+        <v>0.2276847909853985</v>
       </c>
       <c r="T61">
-        <v>3.25003299726614</v>
+        <v>3.331283822197794</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02708074829869269</v>
+        <v>0.02662940249371448</v>
       </c>
       <c r="W61">
-        <v>0.2294143595511683</v>
+        <v>0.2295207868919821</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1805383219912846</v>
+        <v>0.1775293499580965</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2287863885293487</v>
+        <v>0.2306863885293487</v>
       </c>
       <c r="C62">
-        <v>-368.1685340879633</v>
+        <v>-395.6159785638727</v>
       </c>
       <c r="D62">
-        <v>776.3714659120368</v>
+        <v>768.3930214361272</v>
       </c>
       <c r="E62">
-        <v>1118.94</v>
+        <v>1138.409</v>
       </c>
       <c r="F62">
-        <v>1168.14</v>
+        <v>1187.609</v>
       </c>
       <c r="G62">
         <v>23.6</v>
@@ -6365,37 +6365,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M62">
-        <v>275.447412</v>
+        <v>280.0382022</v>
       </c>
       <c r="N62">
-        <v>-226.547412</v>
+        <v>-231.1382022</v>
       </c>
       <c r="O62">
-        <v>-33.98211180000001</v>
+        <v>-34.67073033</v>
       </c>
       <c r="P62">
-        <v>-192.5653002</v>
+        <v>-196.46747187</v>
       </c>
       <c r="Q62">
-        <v>-176.2653002</v>
+        <v>-180.16747187</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2276847909853985</v>
+        <v>0.2323485035747677</v>
       </c>
       <c r="T62">
-        <v>3.331283822197794</v>
+        <v>3.416701356100301</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02662940249371448</v>
+        <v>0.02619285491185031</v>
       </c>
       <c r="W62">
-        <v>0.2295207868919821</v>
+        <v>0.2296237248117857</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1775293499580965</v>
+        <v>0.1746190327456687</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2306863885293487</v>
+        <v>0.2325863885293487</v>
       </c>
       <c r="C63">
-        <v>-395.6159785638727</v>
+        <v>-422.9011088088196</v>
       </c>
       <c r="D63">
-        <v>768.3930214361272</v>
+        <v>760.5768911911804</v>
       </c>
       <c r="E63">
-        <v>1138.409</v>
+        <v>1157.878</v>
       </c>
       <c r="F63">
-        <v>1187.609</v>
+        <v>1207.078</v>
       </c>
       <c r="G63">
         <v>23.6</v>
@@ -6447,37 +6447,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M63">
-        <v>280.0382022</v>
+        <v>284.6289924</v>
       </c>
       <c r="N63">
-        <v>-231.1382022</v>
+        <v>-235.7289924</v>
       </c>
       <c r="O63">
-        <v>-34.67073033</v>
+        <v>-35.35934886</v>
       </c>
       <c r="P63">
-        <v>-196.46747187</v>
+        <v>-200.36964354</v>
       </c>
       <c r="Q63">
-        <v>-180.16747187</v>
+        <v>-184.06964354</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2323485035747677</v>
+        <v>0.2372576747214721</v>
       </c>
       <c r="T63">
-        <v>3.416701356100301</v>
+        <v>3.506614549681888</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02619285491185031</v>
+        <v>0.02577038951004627</v>
       </c>
       <c r="W63">
-        <v>0.2296237248117857</v>
+        <v>0.2297233421535311</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1746190327456687</v>
+        <v>0.1718025967336418</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2325863885293487</v>
+        <v>0.2344863885293487</v>
       </c>
       <c r="C64">
-        <v>-422.9011088088196</v>
+        <v>-450.0288281500852</v>
       </c>
       <c r="D64">
-        <v>760.5768911911804</v>
+        <v>752.9181718499148</v>
       </c>
       <c r="E64">
-        <v>1157.878</v>
+        <v>1177.347</v>
       </c>
       <c r="F64">
-        <v>1207.078</v>
+        <v>1226.547</v>
       </c>
       <c r="G64">
         <v>23.6</v>
@@ -6529,37 +6529,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M64">
-        <v>284.6289924</v>
+        <v>289.2197826</v>
       </c>
       <c r="N64">
-        <v>-235.7289924</v>
+        <v>-240.3197826</v>
       </c>
       <c r="O64">
-        <v>-35.35934886</v>
+        <v>-36.04796739</v>
       </c>
       <c r="P64">
-        <v>-200.36964354</v>
+        <v>-204.27181521</v>
       </c>
       <c r="Q64">
-        <v>-184.06964354</v>
+        <v>-187.97181521</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2372576747214721</v>
+        <v>0.2424322064707011</v>
       </c>
       <c r="T64">
-        <v>3.506614549681888</v>
+        <v>3.601387915889507</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02577038951004627</v>
+        <v>0.0253613357082995</v>
       </c>
       <c r="W64">
-        <v>0.2297233421535311</v>
+        <v>0.229819797039983</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1718025967336418</v>
+        <v>0.1690755713886634</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2344863885293487</v>
+        <v>0.2363863885293487</v>
       </c>
       <c r="C65">
-        <v>-450.0288281500852</v>
+        <v>-477.0038443853135</v>
       </c>
       <c r="D65">
-        <v>752.9181718499148</v>
+        <v>745.4121556146865</v>
       </c>
       <c r="E65">
-        <v>1177.347</v>
+        <v>1196.816</v>
       </c>
       <c r="F65">
-        <v>1226.547</v>
+        <v>1246.016</v>
       </c>
       <c r="G65">
         <v>23.6</v>
@@ -6611,37 +6611,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M65">
-        <v>289.2197826</v>
+        <v>293.8105728</v>
       </c>
       <c r="N65">
-        <v>-240.3197826</v>
+        <v>-244.9105728</v>
       </c>
       <c r="O65">
-        <v>-36.04796739</v>
+        <v>-36.73658592</v>
       </c>
       <c r="P65">
-        <v>-204.27181521</v>
+        <v>-208.17398688</v>
       </c>
       <c r="Q65">
-        <v>-187.97181521</v>
+        <v>-191.87398688</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2424322064707011</v>
+        <v>0.2478942122059984</v>
       </c>
       <c r="T65">
-        <v>3.601387915889507</v>
+        <v>3.70142646910866</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0253613357082995</v>
+        <v>0.02496506483785732</v>
       </c>
       <c r="W65">
-        <v>0.229819797039983</v>
+        <v>0.2299132377112333</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1690755713886634</v>
+        <v>0.1664337655857155</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2363863885293487</v>
+        <v>0.2382863885293487</v>
       </c>
       <c r="C66">
-        <v>-477.0038443853135</v>
+        <v>-503.8306794327094</v>
       </c>
       <c r="D66">
-        <v>745.4121556146865</v>
+        <v>738.0543205672907</v>
       </c>
       <c r="E66">
-        <v>1196.816</v>
+        <v>1216.285</v>
       </c>
       <c r="F66">
-        <v>1246.016</v>
+        <v>1265.485</v>
       </c>
       <c r="G66">
         <v>23.6</v>
@@ -6693,37 +6693,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M66">
-        <v>293.8105728</v>
+        <v>298.4013630000001</v>
       </c>
       <c r="N66">
-        <v>-244.9105728</v>
+        <v>-249.5013630000001</v>
       </c>
       <c r="O66">
-        <v>-36.73658592</v>
+        <v>-37.42520445000001</v>
       </c>
       <c r="P66">
-        <v>-208.17398688</v>
+        <v>-212.0761585500001</v>
       </c>
       <c r="Q66">
-        <v>-191.87398688</v>
+        <v>-195.77615855</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2478942122059984</v>
+        <v>0.2536683325547411</v>
       </c>
       <c r="T66">
-        <v>3.70142646910866</v>
+        <v>3.807181511083193</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02496506483785732</v>
+        <v>0.0245809869172749</v>
       </c>
       <c r="W66">
-        <v>0.2299132377112333</v>
+        <v>0.2300038032849066</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1664337655857155</v>
+        <v>0.1638732461151661</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2382863885293487</v>
+        <v>0.2401863885293487</v>
       </c>
       <c r="C67">
-        <v>-503.8306794327094</v>
+        <v>-530.5136784152884</v>
       </c>
       <c r="D67">
-        <v>738.0543205672907</v>
+        <v>730.8403215847118</v>
       </c>
       <c r="E67">
-        <v>1216.285</v>
+        <v>1235.754</v>
       </c>
       <c r="F67">
-        <v>1265.485</v>
+        <v>1284.954</v>
       </c>
       <c r="G67">
         <v>23.6</v>
@@ -6775,37 +6775,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M67">
-        <v>298.4013630000001</v>
+        <v>302.9921532000001</v>
       </c>
       <c r="N67">
-        <v>-249.5013630000001</v>
+        <v>-254.0921532000001</v>
       </c>
       <c r="O67">
-        <v>-37.42520445000001</v>
+        <v>-38.11382298000001</v>
       </c>
       <c r="P67">
-        <v>-212.0761585500001</v>
+        <v>-215.9783302200001</v>
       </c>
       <c r="Q67">
-        <v>-195.77615855</v>
+        <v>-199.67833022</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2536683325547411</v>
+        <v>0.2597821070416453</v>
       </c>
       <c r="T67">
-        <v>3.807181511083193</v>
+        <v>3.919157437879758</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0245809869172749</v>
+        <v>0.02420854772155861</v>
       </c>
       <c r="W67">
-        <v>0.2300038032849066</v>
+        <v>0.2300916244472565</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1638732461151661</v>
+        <v>0.1613903181437241</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2401863885293487</v>
+        <v>0.2420863885293487</v>
       </c>
       <c r="C68">
-        <v>-530.5136784152884</v>
+        <v>-557.0570182175275</v>
       </c>
       <c r="D68">
-        <v>730.8403215847118</v>
+        <v>723.7659817824727</v>
       </c>
       <c r="E68">
-        <v>1235.754</v>
+        <v>1255.223</v>
       </c>
       <c r="F68">
-        <v>1284.954</v>
+        <v>1304.423</v>
       </c>
       <c r="G68">
         <v>23.6</v>
@@ -6857,37 +6857,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M68">
-        <v>302.9921532000001</v>
+        <v>307.5829434000001</v>
       </c>
       <c r="N68">
-        <v>-254.0921532000001</v>
+        <v>-258.6829434000001</v>
       </c>
       <c r="O68">
-        <v>-38.11382298000001</v>
+        <v>-38.80244151000002</v>
       </c>
       <c r="P68">
-        <v>-215.9783302200001</v>
+        <v>-219.8805018900001</v>
       </c>
       <c r="Q68">
-        <v>-199.67833022</v>
+        <v>-203.5805018900001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2597821070416453</v>
+        <v>0.2662664133156346</v>
       </c>
       <c r="T68">
-        <v>3.919157437879758</v>
+        <v>4.037919784482175</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02420854772155861</v>
+        <v>0.02384722611377416</v>
       </c>
       <c r="W68">
-        <v>0.2300916244472565</v>
+        <v>0.2301768240823721</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1613903181437241</v>
+        <v>0.1589815074251609</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2420863885293487</v>
+        <v>0.2439863885293487</v>
       </c>
       <c r="C69">
-        <v>-557.0570182175275</v>
+        <v>-583.464715549827</v>
       </c>
       <c r="D69">
-        <v>723.7659817824727</v>
+        <v>716.827284450173</v>
       </c>
       <c r="E69">
-        <v>1255.223</v>
+        <v>1274.692</v>
       </c>
       <c r="F69">
-        <v>1304.423</v>
+        <v>1323.892</v>
       </c>
       <c r="G69">
         <v>23.6</v>
@@ -6939,37 +6939,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M69">
-        <v>307.5829434000001</v>
+        <v>312.1737336</v>
       </c>
       <c r="N69">
-        <v>-258.6829434000001</v>
+        <v>-263.2737336</v>
       </c>
       <c r="O69">
-        <v>-38.80244151000002</v>
+        <v>-39.49106004</v>
       </c>
       <c r="P69">
-        <v>-219.8805018900001</v>
+        <v>-223.78267356</v>
       </c>
       <c r="Q69">
-        <v>-203.5805018900001</v>
+        <v>-207.48267356</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2662664133156346</v>
+        <v>0.2731559887317482</v>
       </c>
       <c r="T69">
-        <v>4.037919784482175</v>
+        <v>4.164104777747244</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02384722611377416</v>
+        <v>0.02349653161210101</v>
       </c>
       <c r="W69">
-        <v>0.2301768240823721</v>
+        <v>0.2302595178458666</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1589815074251609</v>
+        <v>0.1566435440806735</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2439863885293487</v>
+        <v>0.2458863885293487</v>
       </c>
       <c r="C70">
-        <v>-583.464715549827</v>
+        <v>-609.7406345534932</v>
       </c>
       <c r="D70">
-        <v>716.827284450173</v>
+        <v>710.0203654465068</v>
       </c>
       <c r="E70">
-        <v>1274.692</v>
+        <v>1294.161</v>
       </c>
       <c r="F70">
-        <v>1323.892</v>
+        <v>1343.361</v>
       </c>
       <c r="G70">
         <v>23.6</v>
@@ -7021,37 +7021,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M70">
-        <v>312.1737336</v>
+        <v>316.7645238000001</v>
       </c>
       <c r="N70">
-        <v>-263.2737336</v>
+        <v>-267.8645238</v>
       </c>
       <c r="O70">
-        <v>-39.49106004</v>
+        <v>-40.17967857</v>
       </c>
       <c r="P70">
-        <v>-223.78267356</v>
+        <v>-227.68484523</v>
       </c>
       <c r="Q70">
-        <v>-207.48267356</v>
+        <v>-211.38484523</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2731559887317482</v>
+        <v>0.2804900528843852</v>
       </c>
       <c r="T70">
-        <v>4.164104777747244</v>
+        <v>4.298430738319735</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02349653161210101</v>
+        <v>0.02315600216844737</v>
       </c>
       <c r="W70">
-        <v>0.2302595178458666</v>
+        <v>0.2303398146886801</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1566435440806735</v>
+        <v>0.1543733477896493</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2458863885293487</v>
+        <v>0.2477863885293487</v>
       </c>
       <c r="C71">
-        <v>-609.7406345534932</v>
+        <v>-635.8884939764998</v>
       </c>
       <c r="D71">
-        <v>710.0203654465068</v>
+        <v>703.3415060235003</v>
       </c>
       <c r="E71">
-        <v>1294.161</v>
+        <v>1313.63</v>
       </c>
       <c r="F71">
-        <v>1343.361</v>
+        <v>1362.83</v>
       </c>
       <c r="G71">
         <v>23.6</v>
@@ -7103,37 +7103,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M71">
-        <v>316.7645238000001</v>
+        <v>321.355314</v>
       </c>
       <c r="N71">
-        <v>-267.8645238</v>
+        <v>-272.455314</v>
       </c>
       <c r="O71">
-        <v>-40.17967857</v>
+        <v>-40.86829710000001</v>
       </c>
       <c r="P71">
-        <v>-227.68484523</v>
+        <v>-231.5870169</v>
       </c>
       <c r="Q71">
-        <v>-211.38484523</v>
+        <v>-215.2870169</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2804900528843852</v>
+        <v>0.2883130546471981</v>
       </c>
       <c r="T71">
-        <v>4.298430738319735</v>
+        <v>4.441711762930393</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02315600216844737</v>
+        <v>0.02282520213746956</v>
       </c>
       <c r="W71">
-        <v>0.2303398146886801</v>
+        <v>0.2304178173359847</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1543733477896493</v>
+        <v>0.152168014249797</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2477863885293487</v>
+        <v>0.2496863885293487</v>
       </c>
       <c r="C72">
-        <v>-635.8884939764998</v>
+        <v>-661.9118739480317</v>
       </c>
       <c r="D72">
-        <v>703.3415060235003</v>
+        <v>696.7871260519685</v>
       </c>
       <c r="E72">
-        <v>1313.63</v>
+        <v>1333.099</v>
       </c>
       <c r="F72">
-        <v>1362.83</v>
+        <v>1382.299</v>
       </c>
       <c r="G72">
         <v>23.6</v>
@@ -7185,37 +7185,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M72">
-        <v>321.355314</v>
+        <v>325.9461042</v>
       </c>
       <c r="N72">
-        <v>-272.455314</v>
+        <v>-277.0461042000001</v>
       </c>
       <c r="O72">
-        <v>-40.86829710000001</v>
+        <v>-41.55691563000001</v>
       </c>
       <c r="P72">
-        <v>-231.5870169</v>
+        <v>-235.4891885700001</v>
       </c>
       <c r="Q72">
-        <v>-215.2870169</v>
+        <v>-219.1891885700001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2883130546471981</v>
+        <v>0.2966755737729636</v>
       </c>
       <c r="T72">
-        <v>4.441711762930393</v>
+        <v>4.5948742375142</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02282520213746956</v>
+        <v>0.0225037204172235</v>
       </c>
       <c r="W72">
-        <v>0.2304178173359847</v>
+        <v>0.2304936227256187</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.152168014249797</v>
+        <v>0.15002480278149</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2496863885293487</v>
+        <v>0.2515863885293487</v>
       </c>
       <c r="C73">
-        <v>-661.9118739480313</v>
+        <v>-687.8142223777304</v>
       </c>
       <c r="D73">
-        <v>696.7871260519687</v>
+        <v>690.3537776222696</v>
       </c>
       <c r="E73">
-        <v>1333.099</v>
+        <v>1352.568</v>
       </c>
       <c r="F73">
-        <v>1382.299</v>
+        <v>1401.768</v>
       </c>
       <c r="G73">
         <v>23.6</v>
@@ -7267,37 +7267,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M73">
-        <v>325.9461042</v>
+        <v>330.5368944</v>
       </c>
       <c r="N73">
-        <v>-277.0461042000001</v>
+        <v>-281.6368944</v>
       </c>
       <c r="O73">
-        <v>-41.55691563000001</v>
+        <v>-42.24553415999999</v>
       </c>
       <c r="P73">
-        <v>-235.4891885700001</v>
+        <v>-239.39136024</v>
       </c>
       <c r="Q73">
-        <v>-219.1891885700001</v>
+        <v>-223.09136024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2966755737729634</v>
+        <v>0.3056354156934264</v>
       </c>
       <c r="T73">
-        <v>4.594874237514198</v>
+        <v>4.758976888853991</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0225037204172235</v>
+        <v>0.02219116874476207</v>
       </c>
       <c r="W73">
-        <v>0.2304936227256187</v>
+        <v>0.2305673224099851</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.15002480278149</v>
+        <v>0.1479411249650806</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2515863885293487</v>
+        <v>0.2534863885293487</v>
       </c>
       <c r="C74">
-        <v>-687.8142223777304</v>
+        <v>-713.5988610036917</v>
       </c>
       <c r="D74">
-        <v>690.3537776222696</v>
+        <v>684.0381389963084</v>
       </c>
       <c r="E74">
-        <v>1352.568</v>
+        <v>1372.037</v>
       </c>
       <c r="F74">
-        <v>1401.768</v>
+        <v>1421.237</v>
       </c>
       <c r="G74">
         <v>23.6</v>
@@ -7349,37 +7349,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M74">
-        <v>330.5368944</v>
+        <v>335.1276846</v>
       </c>
       <c r="N74">
-        <v>-281.6368944</v>
+        <v>-286.2276846</v>
       </c>
       <c r="O74">
-        <v>-42.24553415999999</v>
+        <v>-42.93415269</v>
       </c>
       <c r="P74">
-        <v>-239.39136024</v>
+        <v>-243.29353191</v>
       </c>
       <c r="Q74">
-        <v>-223.09136024</v>
+        <v>-226.99353191</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3056354156934264</v>
+        <v>0.3152589496079978</v>
       </c>
       <c r="T74">
-        <v>4.758976888853991</v>
+        <v>4.935235292144879</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02219116874476207</v>
+        <v>0.02188718013182012</v>
       </c>
       <c r="W74">
-        <v>0.2305673224099851</v>
+        <v>0.2306390029249168</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1479411249650806</v>
+        <v>0.1459145342121342</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2534863885293487</v>
+        <v>0.2553863885293487</v>
       </c>
       <c r="C75">
-        <v>-713.5988610036917</v>
+        <v>-739.2689911114848</v>
       </c>
       <c r="D75">
-        <v>684.0381389963084</v>
+        <v>677.8370088885154</v>
       </c>
       <c r="E75">
-        <v>1372.037</v>
+        <v>1391.506</v>
       </c>
       <c r="F75">
-        <v>1421.237</v>
+        <v>1440.706</v>
       </c>
       <c r="G75">
         <v>23.6</v>
@@ -7431,37 +7431,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M75">
-        <v>335.1276846</v>
+        <v>339.7184748</v>
       </c>
       <c r="N75">
-        <v>-286.2276846</v>
+        <v>-290.8184748</v>
       </c>
       <c r="O75">
-        <v>-42.93415269</v>
+        <v>-43.62277122</v>
       </c>
       <c r="P75">
-        <v>-243.29353191</v>
+        <v>-247.19570358</v>
       </c>
       <c r="Q75">
-        <v>-226.99353191</v>
+        <v>-230.89570358</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3152589496079978</v>
+        <v>0.3256227553621515</v>
       </c>
       <c r="T75">
-        <v>4.935235292144879</v>
+        <v>5.125052034150452</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02188718013182012</v>
+        <v>0.02159140742733607</v>
       </c>
       <c r="W75">
-        <v>0.2306390029249168</v>
+        <v>0.2307087461286342</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1459145342121342</v>
+        <v>0.1439427161822405</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2553863885293487</v>
+        <v>0.2572863885293487</v>
       </c>
       <c r="C76">
-        <v>-739.2689911114848</v>
+        <v>-764.8276989449017</v>
       </c>
       <c r="D76">
-        <v>677.8370088885154</v>
+        <v>671.7473010550984</v>
       </c>
       <c r="E76">
-        <v>1391.506</v>
+        <v>1410.975</v>
       </c>
       <c r="F76">
-        <v>1440.706</v>
+        <v>1460.175</v>
       </c>
       <c r="G76">
         <v>23.6</v>
@@ -7513,37 +7513,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M76">
-        <v>339.7184748</v>
+        <v>344.309265</v>
       </c>
       <c r="N76">
-        <v>-290.8184748</v>
+        <v>-295.409265</v>
       </c>
       <c r="O76">
-        <v>-43.62277122</v>
+        <v>-44.31138975</v>
       </c>
       <c r="P76">
-        <v>-247.19570358</v>
+        <v>-251.09787525</v>
       </c>
       <c r="Q76">
-        <v>-230.89570358</v>
+        <v>-234.79787525</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3256227553621515</v>
+        <v>0.3368156655766376</v>
       </c>
       <c r="T76">
-        <v>5.125052034150452</v>
+        <v>5.33005411551647</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02159140742733607</v>
+        <v>0.02130352199497159</v>
       </c>
       <c r="W76">
-        <v>0.2307087461286342</v>
+        <v>0.2307766295135857</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1439427161822405</v>
+        <v>0.1420234799664774</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2572863885293487</v>
+        <v>0.2591863885293487</v>
       </c>
       <c r="C77">
-        <v>-764.8276989449017</v>
+        <v>-790.2779608276346</v>
       </c>
       <c r="D77">
-        <v>671.7473010550984</v>
+        <v>665.7660391723654</v>
       </c>
       <c r="E77">
-        <v>1410.975</v>
+        <v>1430.444</v>
       </c>
       <c r="F77">
-        <v>1460.175</v>
+        <v>1479.644</v>
       </c>
       <c r="G77">
         <v>23.6</v>
@@ -7595,37 +7595,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M77">
-        <v>344.309265</v>
+        <v>348.9000552</v>
       </c>
       <c r="N77">
-        <v>-295.409265</v>
+        <v>-300.0000552</v>
       </c>
       <c r="O77">
-        <v>-44.31138975</v>
+        <v>-45.00000828</v>
       </c>
       <c r="P77">
-        <v>-251.09787525</v>
+        <v>-255.00004692</v>
       </c>
       <c r="Q77">
-        <v>-234.79787525</v>
+        <v>-238.70004692</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3368156655766376</v>
+        <v>0.3489413183089975</v>
       </c>
       <c r="T77">
-        <v>5.33005411551647</v>
+        <v>5.55213970366299</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02130352199497159</v>
+        <v>0.02102321249503775</v>
       </c>
       <c r="W77">
-        <v>0.2307766295135857</v>
+        <v>0.2308427264936701</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1420234799664774</v>
+        <v>0.1401547499669182</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2591863885293487</v>
+        <v>0.2610863885293487</v>
       </c>
       <c r="C78">
-        <v>-790.2779608276346</v>
+        <v>-815.6226480137525</v>
       </c>
       <c r="D78">
-        <v>665.7660391723654</v>
+        <v>659.8903519862475</v>
       </c>
       <c r="E78">
-        <v>1430.444</v>
+        <v>1449.913</v>
       </c>
       <c r="F78">
-        <v>1479.644</v>
+        <v>1499.113</v>
       </c>
       <c r="G78">
         <v>23.6</v>
@@ -7677,37 +7677,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M78">
-        <v>348.9000552</v>
+        <v>353.4908454</v>
       </c>
       <c r="N78">
-        <v>-300.0000552</v>
+        <v>-304.5908454</v>
       </c>
       <c r="O78">
-        <v>-45.00000828</v>
+        <v>-45.68862681</v>
       </c>
       <c r="P78">
-        <v>-255.00004692</v>
+        <v>-258.90221859</v>
       </c>
       <c r="Q78">
-        <v>-238.70004692</v>
+        <v>-242.60221859</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3489413183089975</v>
+        <v>0.36212137562678</v>
       </c>
       <c r="T78">
-        <v>5.55213970366299</v>
+        <v>5.79353708208312</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02102321249503775</v>
+        <v>0.02075018376133596</v>
       </c>
       <c r="W78">
-        <v>0.2308427264936701</v>
+        <v>0.230907106669077</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1401547499669182</v>
+        <v>0.1383345584089063</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2610863885293487</v>
+        <v>0.2629863885293486</v>
       </c>
       <c r="C79">
-        <v>-815.6226480137525</v>
+        <v>-840.8645312835732</v>
       </c>
       <c r="D79">
-        <v>659.8903519862475</v>
+        <v>654.1174687164269</v>
       </c>
       <c r="E79">
-        <v>1449.913</v>
+        <v>1469.382</v>
       </c>
       <c r="F79">
-        <v>1499.113</v>
+        <v>1518.582</v>
       </c>
       <c r="G79">
         <v>23.6</v>
@@ -7759,37 +7759,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M79">
-        <v>353.4908454</v>
+        <v>358.0816356</v>
       </c>
       <c r="N79">
-        <v>-304.5908454</v>
+        <v>-309.1816356</v>
       </c>
       <c r="O79">
-        <v>-45.68862681</v>
+        <v>-46.37724534000001</v>
       </c>
       <c r="P79">
-        <v>-258.90221859</v>
+        <v>-262.80439026</v>
       </c>
       <c r="Q79">
-        <v>-242.60221859</v>
+        <v>-246.50439026</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.36212137562678</v>
+        <v>0.3764996199734518</v>
       </c>
       <c r="T79">
-        <v>5.79353708208312</v>
+        <v>6.056879676723261</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02075018376133596</v>
+        <v>0.02048415576439576</v>
       </c>
       <c r="W79">
-        <v>0.230907106669077</v>
+        <v>0.2309698360707555</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1383345584089063</v>
+        <v>0.136561038429305</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2629863885293486</v>
+        <v>0.2648863885293488</v>
       </c>
       <c r="C80">
-        <v>-840.8645312835732</v>
+        <v>-866.0062853003972</v>
       </c>
       <c r="D80">
-        <v>654.1174687164269</v>
+        <v>648.444714699603</v>
       </c>
       <c r="E80">
-        <v>1469.382</v>
+        <v>1488.851</v>
       </c>
       <c r="F80">
-        <v>1518.582</v>
+        <v>1538.051</v>
       </c>
       <c r="G80">
         <v>23.6</v>
@@ -7841,37 +7841,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M80">
-        <v>358.0816356</v>
+        <v>362.6724258</v>
       </c>
       <c r="N80">
-        <v>-309.1816356</v>
+        <v>-313.7724258000001</v>
       </c>
       <c r="O80">
-        <v>-46.37724534000001</v>
+        <v>-47.06586387000001</v>
       </c>
       <c r="P80">
-        <v>-262.80439026</v>
+        <v>-266.7065619300001</v>
       </c>
       <c r="Q80">
-        <v>-246.50439026</v>
+        <v>-250.4065619300001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3764996199734518</v>
+        <v>0.3922472209245687</v>
       </c>
       <c r="T80">
-        <v>6.056879676723261</v>
+        <v>6.345302518471991</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02048415576439576</v>
+        <v>0.02022486265345403</v>
       </c>
       <c r="W80">
-        <v>0.2309698360707555</v>
+        <v>0.2310309773863156</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.136561038429305</v>
+        <v>0.1348324176896935</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2648863885293488</v>
+        <v>0.2667863885293487</v>
       </c>
       <c r="C81">
-        <v>-866.0062853003972</v>
+        <v>-891.0504927424863</v>
       </c>
       <c r="D81">
-        <v>648.444714699603</v>
+        <v>642.8695072575139</v>
       </c>
       <c r="E81">
-        <v>1488.851</v>
+        <v>1508.32</v>
       </c>
       <c r="F81">
-        <v>1538.051</v>
+        <v>1557.52</v>
       </c>
       <c r="G81">
         <v>23.6</v>
@@ -7923,37 +7923,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M81">
-        <v>362.6724258</v>
+        <v>367.2632160000001</v>
       </c>
       <c r="N81">
-        <v>-313.7724258000001</v>
+        <v>-318.3632160000001</v>
       </c>
       <c r="O81">
-        <v>-47.06586387000001</v>
+        <v>-47.75448240000001</v>
       </c>
       <c r="P81">
-        <v>-266.7065619300001</v>
+        <v>-270.6087336000001</v>
       </c>
       <c r="Q81">
-        <v>-250.4065619300001</v>
+        <v>-254.3087336</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3922472209245687</v>
+        <v>0.4095695819707971</v>
       </c>
       <c r="T81">
-        <v>6.345302518471991</v>
+        <v>6.662567644395589</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02022486265345403</v>
+        <v>0.01997205187028586</v>
       </c>
       <c r="W81">
-        <v>0.2310309773863156</v>
+        <v>0.2310905901689866</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1348324176896935</v>
+        <v>0.1331470124685723</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2667863885293487</v>
+        <v>0.2686863885293487</v>
       </c>
       <c r="C82">
-        <v>-891.0504927424863</v>
+        <v>-915.99964822371</v>
       </c>
       <c r="D82">
-        <v>642.8695072575139</v>
+        <v>637.3893517762903</v>
       </c>
       <c r="E82">
-        <v>1508.32</v>
+        <v>1527.789</v>
       </c>
       <c r="F82">
-        <v>1557.52</v>
+        <v>1576.989</v>
       </c>
       <c r="G82">
         <v>23.6</v>
@@ -8005,37 +8005,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M82">
-        <v>367.2632160000001</v>
+        <v>371.8540062000001</v>
       </c>
       <c r="N82">
-        <v>-318.3632160000001</v>
+        <v>-322.9540062000001</v>
       </c>
       <c r="O82">
-        <v>-47.75448240000001</v>
+        <v>-48.44310093000001</v>
       </c>
       <c r="P82">
-        <v>-270.6087336000001</v>
+        <v>-274.5109052700001</v>
       </c>
       <c r="Q82">
-        <v>-254.3087336</v>
+        <v>-258.2109052700001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4095695819707971</v>
+        <v>0.4287153494429443</v>
       </c>
       <c r="T82">
-        <v>6.662567644395589</v>
+        <v>7.013229099363778</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01997205187028586</v>
+        <v>0.01972548332867739</v>
       </c>
       <c r="W82">
-        <v>0.2310905901689866</v>
+        <v>0.2311487310310979</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1331470124685723</v>
+        <v>0.1315032221911825</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2686863885293487</v>
+        <v>0.2705863885293487</v>
       </c>
       <c r="C83">
-        <v>-915.99964822371</v>
+        <v>-940.8561620153505</v>
       </c>
       <c r="D83">
-        <v>637.3893517762903</v>
+        <v>632.0018379846496</v>
       </c>
       <c r="E83">
-        <v>1527.789</v>
+        <v>1547.258</v>
       </c>
       <c r="F83">
-        <v>1576.989</v>
+        <v>1596.458</v>
       </c>
       <c r="G83">
         <v>23.6</v>
@@ -8087,37 +8087,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M83">
-        <v>371.8540062000001</v>
+        <v>376.4447964</v>
       </c>
       <c r="N83">
-        <v>-322.9540062000001</v>
+        <v>-327.5447964</v>
       </c>
       <c r="O83">
-        <v>-48.44310093000001</v>
+        <v>-49.13171946</v>
       </c>
       <c r="P83">
-        <v>-274.5109052700001</v>
+        <v>-278.41307694</v>
       </c>
       <c r="Q83">
-        <v>-258.2109052700001</v>
+        <v>-262.11307694</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4287153494429443</v>
+        <v>0.4499884244119967</v>
       </c>
       <c r="T83">
-        <v>7.013229099363778</v>
+        <v>7.402852938217321</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01972548332867739</v>
+        <v>0.01948492865393742</v>
       </c>
       <c r="W83">
-        <v>0.2311487310310979</v>
+        <v>0.2312054538234015</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1315032221911825</v>
+        <v>0.129899524359583</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2705863885293487</v>
+        <v>0.2724863885293487</v>
       </c>
       <c r="C84">
-        <v>-940.8561620153505</v>
+        <v>-965.622363580743</v>
       </c>
       <c r="D84">
-        <v>632.0018379846496</v>
+        <v>626.7046364192571</v>
       </c>
       <c r="E84">
-        <v>1547.258</v>
+        <v>1566.727</v>
       </c>
       <c r="F84">
-        <v>1596.458</v>
+        <v>1615.927</v>
       </c>
       <c r="G84">
         <v>23.6</v>
@@ -8169,37 +8169,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M84">
-        <v>376.4447964</v>
+        <v>381.0355866</v>
       </c>
       <c r="N84">
-        <v>-327.5447964</v>
+        <v>-332.1355866</v>
       </c>
       <c r="O84">
-        <v>-49.13171946</v>
+        <v>-49.82033799</v>
       </c>
       <c r="P84">
-        <v>-278.41307694</v>
+        <v>-282.31524861</v>
       </c>
       <c r="Q84">
-        <v>-262.11307694</v>
+        <v>-266.01524861</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4499884244119967</v>
+        <v>0.4737642140832908</v>
       </c>
       <c r="T84">
-        <v>7.402852938217321</v>
+        <v>7.838314875759519</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01948492865393742</v>
+        <v>0.01925017047738396</v>
       </c>
       <c r="W84">
-        <v>0.2312054538234015</v>
+        <v>0.2312608098014329</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.129899524359583</v>
+        <v>0.1283344698492265</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2724863885293487</v>
+        <v>0.2743863885293487</v>
       </c>
       <c r="C85">
-        <v>-965.622363580743</v>
+        <v>-990.3005049336356</v>
       </c>
       <c r="D85">
-        <v>626.7046364192571</v>
+        <v>621.4954950663646</v>
       </c>
       <c r="E85">
-        <v>1566.727</v>
+        <v>1586.196</v>
       </c>
       <c r="F85">
-        <v>1615.927</v>
+        <v>1635.396</v>
       </c>
       <c r="G85">
         <v>23.6</v>
@@ -8251,37 +8251,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M85">
-        <v>381.0355866</v>
+        <v>385.6263768000001</v>
       </c>
       <c r="N85">
-        <v>-332.1355866</v>
+        <v>-336.7263768</v>
       </c>
       <c r="O85">
-        <v>-49.82033799</v>
+        <v>-50.50895652000001</v>
       </c>
       <c r="P85">
-        <v>-282.31524861</v>
+        <v>-286.21742028</v>
       </c>
       <c r="Q85">
-        <v>-266.01524861</v>
+        <v>-269.91742028</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4737642140832908</v>
+        <v>0.5005119774634964</v>
       </c>
       <c r="T85">
-        <v>7.838314875759519</v>
+        <v>8.328209555494489</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01925017047738396</v>
+        <v>0.01902100178122463</v>
       </c>
       <c r="W85">
-        <v>0.2312608098014329</v>
+        <v>0.2313148477799872</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1283344698492265</v>
+        <v>0.1268066785414976</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2743863885293487</v>
+        <v>0.2762863885293486</v>
       </c>
       <c r="C86">
-        <v>-990.3005049336354</v>
+        <v>-1014.892763830443</v>
       </c>
       <c r="D86">
-        <v>621.4954950663646</v>
+        <v>616.3722361695569</v>
       </c>
       <c r="E86">
-        <v>1586.196</v>
+        <v>1605.665</v>
       </c>
       <c r="F86">
-        <v>1635.396</v>
+        <v>1654.865</v>
       </c>
       <c r="G86">
         <v>23.6</v>
@@ -8333,37 +8333,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M86">
-        <v>385.6263768</v>
+        <v>390.217167</v>
       </c>
       <c r="N86">
-        <v>-336.7263768</v>
+        <v>-341.317167</v>
       </c>
       <c r="O86">
-        <v>-50.50895652000001</v>
+        <v>-51.19757505</v>
       </c>
       <c r="P86">
-        <v>-286.21742028</v>
+        <v>-290.11959195</v>
       </c>
       <c r="Q86">
-        <v>-269.91742028</v>
+        <v>-273.81959195</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5005119774634962</v>
+        <v>0.5308261092943959</v>
       </c>
       <c r="T86">
-        <v>8.328209555494483</v>
+        <v>8.883423525860783</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01902100178122463</v>
+        <v>0.01879722528968081</v>
       </c>
       <c r="W86">
-        <v>0.2313148477799872</v>
+        <v>0.2313676142766933</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1268066785414975</v>
+        <v>0.1253148352645387</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2762863885293486</v>
+        <v>0.2781863885293487</v>
       </c>
       <c r="C87">
-        <v>-1014.892763830443</v>
+        <v>-1039.401246805903</v>
       </c>
       <c r="D87">
-        <v>616.3722361695569</v>
+        <v>611.3327531940974</v>
       </c>
       <c r="E87">
-        <v>1605.665</v>
+        <v>1625.134</v>
       </c>
       <c r="F87">
-        <v>1654.865</v>
+        <v>1674.334</v>
       </c>
       <c r="G87">
         <v>23.6</v>
@@ -8415,37 +8415,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M87">
-        <v>390.217167</v>
+        <v>394.8079572</v>
       </c>
       <c r="N87">
-        <v>-341.317167</v>
+        <v>-345.9079572000001</v>
       </c>
       <c r="O87">
-        <v>-51.19757505</v>
+        <v>-51.88619358</v>
       </c>
       <c r="P87">
-        <v>-290.11959195</v>
+        <v>-294.0217636200001</v>
       </c>
       <c r="Q87">
-        <v>-273.81959195</v>
+        <v>-277.72176362</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5308261092943959</v>
+        <v>0.5654708313868527</v>
       </c>
       <c r="T87">
-        <v>8.883423525860783</v>
+        <v>9.517953777707982</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01879722528968081</v>
+        <v>0.0185786529025915</v>
       </c>
       <c r="W87">
-        <v>0.2313676142766933</v>
+        <v>0.2314191536455689</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1253148352645387</v>
+        <v>0.1238576860172765</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2781863885293487</v>
+        <v>0.2800863885293486</v>
       </c>
       <c r="C88">
-        <v>-1039.401246805903</v>
+        <v>-1063.827992061015</v>
       </c>
       <c r="D88">
-        <v>611.3327531940974</v>
+        <v>606.375007938985</v>
       </c>
       <c r="E88">
-        <v>1625.134</v>
+        <v>1644.603</v>
       </c>
       <c r="F88">
-        <v>1674.334</v>
+        <v>1693.803</v>
       </c>
       <c r="G88">
         <v>23.6</v>
@@ -8497,37 +8497,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M88">
-        <v>394.8079572</v>
+        <v>399.3987474</v>
       </c>
       <c r="N88">
-        <v>-345.9079572000001</v>
+        <v>-350.4987474000001</v>
       </c>
       <c r="O88">
-        <v>-51.88619358</v>
+        <v>-52.57481211000001</v>
       </c>
       <c r="P88">
-        <v>-294.0217636200001</v>
+        <v>-297.92393529</v>
       </c>
       <c r="Q88">
-        <v>-277.72176362</v>
+        <v>-281.62393529</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5654708313868527</v>
+        <v>0.605445510724303</v>
       </c>
       <c r="T88">
-        <v>9.517953777707982</v>
+        <v>10.2501040683009</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0185786529025915</v>
+        <v>0.01836510516807895</v>
       </c>
       <c r="W88">
-        <v>0.2314191536455689</v>
+        <v>0.231469508201367</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1238576860172765</v>
+        <v>0.1224340344538596</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2800863885293486</v>
+        <v>0.2819863885293487</v>
       </c>
       <c r="C89">
-        <v>-1063.827992061015</v>
+        <v>-1088.174972211598</v>
       </c>
       <c r="D89">
-        <v>606.375007938985</v>
+        <v>601.4970277884019</v>
       </c>
       <c r="E89">
-        <v>1644.603</v>
+        <v>1664.072</v>
       </c>
       <c r="F89">
-        <v>1693.803</v>
+        <v>1713.272</v>
       </c>
       <c r="G89">
         <v>23.6</v>
@@ -8579,37 +8579,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M89">
-        <v>399.3987474</v>
+        <v>403.9895376000001</v>
       </c>
       <c r="N89">
-        <v>-350.4987474000001</v>
+        <v>-355.0895376000001</v>
       </c>
       <c r="O89">
-        <v>-52.57481211000001</v>
+        <v>-53.26343064000001</v>
       </c>
       <c r="P89">
-        <v>-297.92393529</v>
+        <v>-301.8261069600001</v>
       </c>
       <c r="Q89">
-        <v>-281.62393529</v>
+        <v>-285.52610696</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.605445510724303</v>
+        <v>0.6520826366179951</v>
       </c>
       <c r="T89">
-        <v>10.2501040683009</v>
+        <v>11.10427940732598</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01836510516807895</v>
+        <v>0.01815641079116896</v>
       </c>
       <c r="W89">
-        <v>0.231469508201367</v>
+        <v>0.2315187183354424</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1224340344538596</v>
+        <v>0.121042738607793</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2819863885293487</v>
+        <v>0.2838863885293487</v>
       </c>
       <c r="C90">
-        <v>-1088.174972211598</v>
+        <v>-1112.444096905233</v>
       </c>
       <c r="D90">
-        <v>601.4970277884019</v>
+        <v>596.6969030947674</v>
       </c>
       <c r="E90">
-        <v>1664.072</v>
+        <v>1683.541</v>
       </c>
       <c r="F90">
-        <v>1713.272</v>
+        <v>1732.741</v>
       </c>
       <c r="G90">
         <v>23.6</v>
@@ -8661,37 +8661,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M90">
-        <v>403.9895376000001</v>
+        <v>408.5803278000001</v>
       </c>
       <c r="N90">
-        <v>-355.0895376000001</v>
+        <v>-359.6803278000001</v>
       </c>
       <c r="O90">
-        <v>-53.26343064000001</v>
+        <v>-53.95204917000002</v>
       </c>
       <c r="P90">
-        <v>-301.8261069600001</v>
+        <v>-305.7282786300001</v>
       </c>
       <c r="Q90">
-        <v>-285.52610696</v>
+        <v>-289.4282786300001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6520826366179951</v>
+        <v>0.7071992399469037</v>
       </c>
       <c r="T90">
-        <v>11.10427940732598</v>
+        <v>12.11375935344653</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01815641079116896</v>
+        <v>0.01795240617553785</v>
       </c>
       <c r="W90">
-        <v>0.2315187183354424</v>
+        <v>0.2315668226238082</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.121042738607793</v>
+        <v>0.1196827078369189</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2838863885293487</v>
+        <v>0.2857863885293487</v>
       </c>
       <c r="C91">
-        <v>-1112.444096905233</v>
+        <v>-1136.637215313895</v>
       </c>
       <c r="D91">
-        <v>596.6969030947674</v>
+        <v>591.9727846861044</v>
       </c>
       <c r="E91">
-        <v>1683.541</v>
+        <v>1703.01</v>
       </c>
       <c r="F91">
-        <v>1732.741</v>
+        <v>1752.21</v>
       </c>
       <c r="G91">
         <v>23.6</v>
@@ -8743,37 +8743,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M91">
-        <v>408.5803278000001</v>
+        <v>413.171118</v>
       </c>
       <c r="N91">
-        <v>-359.6803278000001</v>
+        <v>-364.271118</v>
       </c>
       <c r="O91">
-        <v>-53.95204917000002</v>
+        <v>-54.6406677</v>
       </c>
       <c r="P91">
-        <v>-305.7282786300001</v>
+        <v>-309.6304503</v>
       </c>
       <c r="Q91">
-        <v>-289.4282786300001</v>
+        <v>-293.3304503</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7071992399469037</v>
+        <v>0.7733391639415941</v>
       </c>
       <c r="T91">
-        <v>12.11375935344653</v>
+        <v>13.32513528879118</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01795240617553785</v>
+        <v>0.01775293499580965</v>
       </c>
       <c r="W91">
-        <v>0.2315668226238082</v>
+        <v>0.2316138579279881</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1196827078369189</v>
+        <v>0.1183528999720644</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2857863885293487</v>
+        <v>0.2876863885293487</v>
       </c>
       <c r="C92">
-        <v>-1136.637215313895</v>
+        <v>-1160.756118509119</v>
       </c>
       <c r="D92">
-        <v>591.9727846861044</v>
+        <v>587.3228814908812</v>
       </c>
       <c r="E92">
-        <v>1703.01</v>
+        <v>1722.479</v>
       </c>
       <c r="F92">
-        <v>1752.21</v>
+        <v>1771.679</v>
       </c>
       <c r="G92">
         <v>23.6</v>
@@ -8825,37 +8825,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M92">
-        <v>413.171118</v>
+        <v>417.7619082000001</v>
       </c>
       <c r="N92">
-        <v>-364.271118</v>
+        <v>-368.8619082</v>
       </c>
       <c r="O92">
-        <v>-54.6406677</v>
+        <v>-55.32928623</v>
       </c>
       <c r="P92">
-        <v>-309.6304503</v>
+        <v>-313.53262197</v>
       </c>
       <c r="Q92">
-        <v>-293.3304503</v>
+        <v>-297.23262197</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7733391639415941</v>
+        <v>0.8541768488239936</v>
       </c>
       <c r="T92">
-        <v>13.32513528879118</v>
+        <v>14.80570587643465</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01775293499580965</v>
+        <v>0.0175578477980535</v>
       </c>
       <c r="W92">
-        <v>0.2316138579279881</v>
+        <v>0.231659859489219</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1183528999720644</v>
+        <v>0.1170523186536901</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2876863885293487</v>
+        <v>0.2895863885293486</v>
       </c>
       <c r="C93">
-        <v>-1160.756118509119</v>
+        <v>-1184.802541726077</v>
       </c>
       <c r="D93">
-        <v>587.3228814908812</v>
+        <v>582.7454582739231</v>
       </c>
       <c r="E93">
-        <v>1722.479</v>
+        <v>1741.948</v>
       </c>
       <c r="F93">
-        <v>1771.679</v>
+        <v>1791.148</v>
       </c>
       <c r="G93">
         <v>23.6</v>
@@ -8907,37 +8907,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M93">
-        <v>417.7619082000001</v>
+        <v>422.3526984000001</v>
       </c>
       <c r="N93">
-        <v>-368.8619082</v>
+        <v>-373.4526984</v>
       </c>
       <c r="O93">
-        <v>-55.32928623</v>
+        <v>-56.01790476</v>
       </c>
       <c r="P93">
-        <v>-313.53262197</v>
+        <v>-317.43479364</v>
       </c>
       <c r="Q93">
-        <v>-297.23262197</v>
+        <v>-301.13479364</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8541768488239936</v>
+        <v>0.9552239549269929</v>
       </c>
       <c r="T93">
-        <v>14.80570587643465</v>
+        <v>16.65641911098898</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0175578477980535</v>
+        <v>0.01736700162633553</v>
       </c>
       <c r="W93">
-        <v>0.231659859489219</v>
+        <v>0.2317048610165101</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1170523186536901</v>
+        <v>0.115780010842237</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2895863885293486</v>
+        <v>0.2914863885293487</v>
       </c>
       <c r="C94">
-        <v>-1184.802541726077</v>
+        <v>-1208.778166522624</v>
       </c>
       <c r="D94">
-        <v>582.7454582739231</v>
+        <v>578.2388334773759</v>
       </c>
       <c r="E94">
-        <v>1741.948</v>
+        <v>1761.417</v>
       </c>
       <c r="F94">
-        <v>1791.148</v>
+        <v>1810.617</v>
       </c>
       <c r="G94">
         <v>23.6</v>
@@ -8989,37 +8989,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M94">
-        <v>422.3526984000001</v>
+        <v>426.9434886000001</v>
       </c>
       <c r="N94">
-        <v>-373.4526984</v>
+        <v>-378.0434886</v>
       </c>
       <c r="O94">
-        <v>-56.01790476</v>
+        <v>-56.70652329000001</v>
       </c>
       <c r="P94">
-        <v>-317.43479364</v>
+        <v>-321.33696531</v>
       </c>
       <c r="Q94">
-        <v>-301.13479364</v>
+        <v>-305.03696531</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9552239549269929</v>
+        <v>1.085141662773706</v>
       </c>
       <c r="T94">
-        <v>16.65641911098898</v>
+        <v>19.03590755541598</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01736700162633553</v>
+        <v>0.01718025967336418</v>
       </c>
       <c r="W94">
-        <v>0.2317048610165101</v>
+        <v>0.2317488947690207</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.115780010842237</v>
+        <v>0.1145350644890946</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2914863885293487</v>
+        <v>0.2933863885293487</v>
       </c>
       <c r="C95">
-        <v>-1208.778166522624</v>
+        <v>-1232.684622838914</v>
       </c>
       <c r="D95">
-        <v>578.2388334773759</v>
+        <v>573.8013771610857</v>
       </c>
       <c r="E95">
-        <v>1761.417</v>
+        <v>1780.886</v>
       </c>
       <c r="F95">
-        <v>1810.617</v>
+        <v>1830.086</v>
       </c>
       <c r="G95">
         <v>23.6</v>
@@ -9071,37 +9071,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M95">
-        <v>426.9434886000001</v>
+        <v>431.5342788000001</v>
       </c>
       <c r="N95">
-        <v>-378.0434886</v>
+        <v>-382.6342788000001</v>
       </c>
       <c r="O95">
-        <v>-56.70652329000001</v>
+        <v>-57.39514182000001</v>
       </c>
       <c r="P95">
-        <v>-321.33696531</v>
+        <v>-325.2391369800001</v>
       </c>
       <c r="Q95">
-        <v>-305.03696531</v>
+        <v>-308.9391369800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.085141662773706</v>
+        <v>1.258365273235991</v>
       </c>
       <c r="T95">
-        <v>19.03590755541598</v>
+        <v>22.20855881465198</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01718025967336418</v>
+        <v>0.01699749095343477</v>
       </c>
       <c r="W95">
-        <v>0.2317488947690207</v>
+        <v>0.2317919916331801</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1145350644890946</v>
+        <v>0.1133166063562319</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2933863885293487</v>
+        <v>0.2952863885293487</v>
       </c>
       <c r="C96">
-        <v>-1232.684622838914</v>
+        <v>-1256.523490962913</v>
       </c>
       <c r="D96">
-        <v>573.8013771610857</v>
+        <v>569.4315090370867</v>
       </c>
       <c r="E96">
-        <v>1780.886</v>
+        <v>1800.355</v>
       </c>
       <c r="F96">
-        <v>1830.086</v>
+        <v>1849.555</v>
       </c>
       <c r="G96">
         <v>23.6</v>
@@ -9153,37 +9153,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M96">
-        <v>431.5342788000001</v>
+        <v>436.1250690000001</v>
       </c>
       <c r="N96">
-        <v>-382.6342788000001</v>
+        <v>-387.2250690000001</v>
       </c>
       <c r="O96">
-        <v>-57.39514182000001</v>
+        <v>-58.08376035000001</v>
       </c>
       <c r="P96">
-        <v>-325.2391369800001</v>
+        <v>-329.14130865</v>
       </c>
       <c r="Q96">
-        <v>-308.9391369800001</v>
+        <v>-312.84130865</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.258365273235991</v>
+        <v>1.50087832788319</v>
       </c>
       <c r="T96">
-        <v>22.20855881465198</v>
+        <v>26.65027057758239</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01699749095343477</v>
+        <v>0.01681856999603019</v>
       </c>
       <c r="W96">
-        <v>0.2317919916331801</v>
+        <v>0.2318341811949361</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1133166063562319</v>
+        <v>0.1121237999735347</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2952863885293487</v>
+        <v>0.2971863885293487</v>
       </c>
       <c r="C97">
-        <v>-1256.523490962913</v>
+        <v>-1280.296303406777</v>
       </c>
       <c r="D97">
-        <v>569.4315090370867</v>
+        <v>565.1276965932233</v>
       </c>
       <c r="E97">
-        <v>1800.355</v>
+        <v>1819.824</v>
       </c>
       <c r="F97">
-        <v>1849.555</v>
+        <v>1869.024</v>
       </c>
       <c r="G97">
         <v>23.6</v>
@@ -9235,37 +9235,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M97">
-        <v>436.1250690000001</v>
+        <v>440.7158592000001</v>
       </c>
       <c r="N97">
-        <v>-387.2250690000001</v>
+        <v>-391.8158592000001</v>
       </c>
       <c r="O97">
-        <v>-58.08376035000001</v>
+        <v>-58.77237888000001</v>
       </c>
       <c r="P97">
-        <v>-329.14130865</v>
+        <v>-333.0434803200001</v>
       </c>
       <c r="Q97">
-        <v>-312.84130865</v>
+        <v>-316.7434803200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.50087832788319</v>
+        <v>1.864647909853989</v>
       </c>
       <c r="T97">
-        <v>26.65027057758239</v>
+        <v>33.31283822197801</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01681856999603019</v>
+        <v>0.01664337655857155</v>
       </c>
       <c r="W97">
-        <v>0.2318341811949361</v>
+        <v>0.2318754918074888</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1121237999735347</v>
+        <v>0.1109558437238104</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2971863885293487</v>
+        <v>0.2990863885293487</v>
       </c>
       <c r="C98">
-        <v>-1280.296303406777</v>
+        <v>-1304.004546698773</v>
       </c>
       <c r="D98">
-        <v>565.1276965932233</v>
+        <v>560.8884533012268</v>
       </c>
       <c r="E98">
-        <v>1819.824</v>
+        <v>1839.293</v>
       </c>
       <c r="F98">
-        <v>1869.024</v>
+        <v>1888.493</v>
       </c>
       <c r="G98">
         <v>23.6</v>
@@ -9317,37 +9317,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M98">
-        <v>440.7158592000001</v>
+        <v>445.3066494</v>
       </c>
       <c r="N98">
-        <v>-391.8158592000001</v>
+        <v>-396.4066494</v>
       </c>
       <c r="O98">
-        <v>-58.77237888000001</v>
+        <v>-59.46099741</v>
       </c>
       <c r="P98">
-        <v>-333.0434803200001</v>
+        <v>-336.94565199</v>
       </c>
       <c r="Q98">
-        <v>-316.7434803200001</v>
+        <v>-320.64565199</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.864647909853984</v>
+        <v>2.470930546471978</v>
       </c>
       <c r="T98">
-        <v>33.31283822197791</v>
+        <v>44.41711762930389</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01664337655857155</v>
+        <v>0.01647179535693679</v>
       </c>
       <c r="W98">
-        <v>0.2318754918074888</v>
+        <v>0.2319159506548343</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1109558437238103</v>
+        <v>0.1098119690462454</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2990863885293487</v>
+        <v>0.3009863885293487</v>
       </c>
       <c r="C99">
-        <v>-1304.004546698773</v>
+        <v>-1327.649663095161</v>
       </c>
       <c r="D99">
-        <v>560.8884533012268</v>
+        <v>556.712336904839</v>
       </c>
       <c r="E99">
-        <v>1839.293</v>
+        <v>1858.762</v>
       </c>
       <c r="F99">
-        <v>1888.493</v>
+        <v>1907.962</v>
       </c>
       <c r="G99">
         <v>23.6</v>
@@ -9399,37 +9399,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M99">
-        <v>445.3066494</v>
+        <v>449.8974396</v>
       </c>
       <c r="N99">
-        <v>-396.4066494</v>
+        <v>-400.9974396</v>
       </c>
       <c r="O99">
-        <v>-59.46099741</v>
+        <v>-60.14961594</v>
       </c>
       <c r="P99">
-        <v>-336.94565199</v>
+        <v>-340.84782366</v>
       </c>
       <c r="Q99">
-        <v>-320.64565199</v>
+        <v>-324.54782366</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.470930546471978</v>
+        <v>3.683495819707967</v>
       </c>
       <c r="T99">
-        <v>44.41711762930389</v>
+        <v>66.62567644395583</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01647179535693679</v>
+        <v>0.01630371581247825</v>
       </c>
       <c r="W99">
-        <v>0.2319159506548343</v>
+        <v>0.2319555838114176</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1098119690462454</v>
+        <v>0.1086914387498551</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3009863885293487</v>
+        <v>0.3028863885293487</v>
       </c>
       <c r="C100">
-        <v>-1327.649663095161</v>
+        <v>-1351.233052216149</v>
       </c>
       <c r="D100">
-        <v>556.712336904839</v>
+        <v>552.5979477838512</v>
       </c>
       <c r="E100">
-        <v>1858.762</v>
+        <v>1878.231</v>
       </c>
       <c r="F100">
-        <v>1907.962</v>
+        <v>1927.431</v>
       </c>
       <c r="G100">
         <v>23.6</v>
@@ -9481,37 +9481,37 @@
         <v>48.90000000000001</v>
       </c>
       <c r="M100">
-        <v>449.8974396</v>
+        <v>454.4882298000001</v>
       </c>
       <c r="N100">
-        <v>-400.9974396</v>
+        <v>-405.5882298</v>
       </c>
       <c r="O100">
-        <v>-60.14961594</v>
+        <v>-60.83823447</v>
       </c>
       <c r="P100">
-        <v>-340.84782366</v>
+        <v>-344.74999533</v>
       </c>
       <c r="Q100">
-        <v>-324.54782366</v>
+        <v>-328.44999533</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.683495819707967</v>
+        <v>7.321191639415934</v>
       </c>
       <c r="T100">
-        <v>66.62567644395583</v>
+        <v>133.2513528879117</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01630371581247825</v>
+        <v>0.01613903181437241</v>
       </c>
       <c r="W100">
-        <v>0.2319555838114176</v>
+        <v>0.231994416298171</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1086914387498551</v>
+        <v>0.1075935454291495</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3028863885293487</v>
-      </c>
-      <c r="C101">
-        <v>-1351.233052216149</v>
-      </c>
-      <c r="D101">
-        <v>552.5979477838512</v>
-      </c>
-      <c r="E101">
-        <v>1878.231</v>
-      </c>
-      <c r="F101">
-        <v>1927.431</v>
-      </c>
-      <c r="G101">
-        <v>23.6</v>
-      </c>
-      <c r="H101">
-        <v>1897.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>65.2</v>
-      </c>
-      <c r="K101">
-        <v>16.3</v>
-      </c>
-      <c r="L101">
-        <v>48.90000000000001</v>
-      </c>
-      <c r="M101">
-        <v>454.4882298000001</v>
-      </c>
-      <c r="N101">
-        <v>-405.5882298</v>
-      </c>
-      <c r="O101">
-        <v>-60.83823447</v>
-      </c>
-      <c r="P101">
-        <v>-344.74999533</v>
-      </c>
-      <c r="Q101">
-        <v>-328.44999533</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.321191639415934</v>
-      </c>
-      <c r="T101">
-        <v>133.2513528879117</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01613903181437241</v>
-      </c>
-      <c r="W101">
-        <v>0.231994416298171</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1075935454291495</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
